--- a/analysis/regression_workbook.xlsx
+++ b/analysis/regression_workbook.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayubi\Downloads\ayushkumar_bitsom_ba_2511507_part3_regression_insights\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayubi\Downloads\ayushkumar_bitsom_ba_2511507_part3_regression_insights\analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3817EEC-EB60-4554-A907-AD247250F920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0164145-0A4A-4DC8-9C8B-501B7C5ADC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="original_data" sheetId="1" r:id="rId1"/>
@@ -442,6 +442,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="[$-14009]yyyy/mm/dd;@"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -513,17 +516,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -806,12 +810,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N321"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -855,7 +862,7 @@
       <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="5">
         <v>45658</v>
       </c>
       <c r="C2" t="s">
@@ -899,7 +906,7 @@
       <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="5">
         <v>45689</v>
       </c>
       <c r="C3" t="s">
@@ -943,7 +950,7 @@
       <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="5">
         <v>45717</v>
       </c>
       <c r="C4" t="s">
@@ -987,7 +994,7 @@
       <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="5">
         <v>45748</v>
       </c>
       <c r="C5" t="s">
@@ -1031,7 +1038,7 @@
       <c r="A6" t="s">
         <v>17</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="5">
         <v>45658</v>
       </c>
       <c r="C6" t="s">
@@ -1075,7 +1082,7 @@
       <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="5">
         <v>45689</v>
       </c>
       <c r="C7" t="s">
@@ -1119,7 +1126,7 @@
       <c r="A8" t="s">
         <v>17</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="5">
         <v>45717</v>
       </c>
       <c r="C8" t="s">
@@ -1163,7 +1170,7 @@
       <c r="A9" t="s">
         <v>17</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="5">
         <v>45748</v>
       </c>
       <c r="C9" t="s">
@@ -1207,7 +1214,7 @@
       <c r="A10" t="s">
         <v>19</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="5">
         <v>45658</v>
       </c>
       <c r="C10" t="s">
@@ -1251,7 +1258,7 @@
       <c r="A11" t="s">
         <v>19</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="5">
         <v>45689</v>
       </c>
       <c r="C11" t="s">
@@ -1295,7 +1302,7 @@
       <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="5">
         <v>45717</v>
       </c>
       <c r="C12" t="s">
@@ -1339,7 +1346,7 @@
       <c r="A13" t="s">
         <v>19</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="5">
         <v>45748</v>
       </c>
       <c r="C13" t="s">
@@ -1383,7 +1390,7 @@
       <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="5">
         <v>45658</v>
       </c>
       <c r="C14" t="s">
@@ -1427,7 +1434,7 @@
       <c r="A15" t="s">
         <v>22</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="5">
         <v>45689</v>
       </c>
       <c r="C15" t="s">
@@ -1471,7 +1478,7 @@
       <c r="A16" t="s">
         <v>22</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="5">
         <v>45717</v>
       </c>
       <c r="C16" t="s">
@@ -1515,7 +1522,7 @@
       <c r="A17" t="s">
         <v>22</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="5">
         <v>45748</v>
       </c>
       <c r="C17" t="s">
@@ -1559,7 +1566,7 @@
       <c r="A18" t="s">
         <v>23</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="5">
         <v>45658</v>
       </c>
       <c r="C18" t="s">
@@ -1603,7 +1610,7 @@
       <c r="A19" t="s">
         <v>23</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="5">
         <v>45689</v>
       </c>
       <c r="C19" t="s">
@@ -1647,7 +1654,7 @@
       <c r="A20" t="s">
         <v>23</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="5">
         <v>45717</v>
       </c>
       <c r="C20" t="s">
@@ -1691,7 +1698,7 @@
       <c r="A21" t="s">
         <v>23</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="5">
         <v>45748</v>
       </c>
       <c r="C21" t="s">
@@ -1735,7 +1742,7 @@
       <c r="A22" t="s">
         <v>25</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="5">
         <v>45658</v>
       </c>
       <c r="C22" t="s">
@@ -1779,7 +1786,7 @@
       <c r="A23" t="s">
         <v>25</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="5">
         <v>45689</v>
       </c>
       <c r="C23" t="s">
@@ -1823,7 +1830,7 @@
       <c r="A24" t="s">
         <v>25</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="5">
         <v>45717</v>
       </c>
       <c r="C24" t="s">
@@ -1867,7 +1874,7 @@
       <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="5">
         <v>45748</v>
       </c>
       <c r="C25" t="s">
@@ -1911,7 +1918,7 @@
       <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="5">
         <v>45658</v>
       </c>
       <c r="C26" t="s">
@@ -1955,7 +1962,7 @@
       <c r="A27" t="s">
         <v>26</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="5">
         <v>45689</v>
       </c>
       <c r="C27" t="s">
@@ -1999,7 +2006,7 @@
       <c r="A28" t="s">
         <v>26</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="5">
         <v>45717</v>
       </c>
       <c r="C28" t="s">
@@ -2043,7 +2050,7 @@
       <c r="A29" t="s">
         <v>26</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="5">
         <v>45748</v>
       </c>
       <c r="C29" t="s">
@@ -2087,7 +2094,7 @@
       <c r="A30" t="s">
         <v>29</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="5">
         <v>45658</v>
       </c>
       <c r="C30" t="s">
@@ -2131,7 +2138,7 @@
       <c r="A31" t="s">
         <v>29</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="5">
         <v>45689</v>
       </c>
       <c r="C31" t="s">
@@ -2175,7 +2182,7 @@
       <c r="A32" t="s">
         <v>29</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="5">
         <v>45717</v>
       </c>
       <c r="C32" t="s">
@@ -2219,7 +2226,7 @@
       <c r="A33" t="s">
         <v>29</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="5">
         <v>45748</v>
       </c>
       <c r="C33" t="s">
@@ -2263,7 +2270,7 @@
       <c r="A34" t="s">
         <v>30</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="5">
         <v>45658</v>
       </c>
       <c r="C34" t="s">
@@ -2307,7 +2314,7 @@
       <c r="A35" t="s">
         <v>30</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="5">
         <v>45689</v>
       </c>
       <c r="C35" t="s">
@@ -2348,7 +2355,7 @@
       <c r="A36" t="s">
         <v>30</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="5">
         <v>45717</v>
       </c>
       <c r="C36" t="s">
@@ -2392,7 +2399,7 @@
       <c r="A37" t="s">
         <v>30</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="5">
         <v>45748</v>
       </c>
       <c r="C37" t="s">
@@ -2436,7 +2443,7 @@
       <c r="A38" t="s">
         <v>31</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="5">
         <v>45658</v>
       </c>
       <c r="C38" t="s">
@@ -2480,7 +2487,7 @@
       <c r="A39" t="s">
         <v>31</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="5">
         <v>45689</v>
       </c>
       <c r="C39" t="s">
@@ -2524,7 +2531,7 @@
       <c r="A40" t="s">
         <v>31</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="5">
         <v>45717</v>
       </c>
       <c r="C40" t="s">
@@ -2568,7 +2575,7 @@
       <c r="A41" t="s">
         <v>31</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="5">
         <v>45748</v>
       </c>
       <c r="C41" t="s">
@@ -2612,7 +2619,7 @@
       <c r="A42" t="s">
         <v>32</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="5">
         <v>45658</v>
       </c>
       <c r="C42" t="s">
@@ -2656,7 +2663,7 @@
       <c r="A43" t="s">
         <v>32</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="5">
         <v>45689</v>
       </c>
       <c r="C43" t="s">
@@ -2700,7 +2707,7 @@
       <c r="A44" t="s">
         <v>32</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="5">
         <v>45717</v>
       </c>
       <c r="C44" t="s">
@@ -2744,7 +2751,7 @@
       <c r="A45" t="s">
         <v>32</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="5">
         <v>45748</v>
       </c>
       <c r="C45" t="s">
@@ -2788,7 +2795,7 @@
       <c r="A46" t="s">
         <v>33</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="5">
         <v>45658</v>
       </c>
       <c r="C46" t="s">
@@ -2832,7 +2839,7 @@
       <c r="A47" t="s">
         <v>33</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="5">
         <v>45689</v>
       </c>
       <c r="C47" t="s">
@@ -2876,7 +2883,7 @@
       <c r="A48" t="s">
         <v>33</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="5">
         <v>45717</v>
       </c>
       <c r="C48" t="s">
@@ -2920,7 +2927,7 @@
       <c r="A49" t="s">
         <v>33</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="5">
         <v>45748</v>
       </c>
       <c r="C49" t="s">
@@ -2964,7 +2971,7 @@
       <c r="A50" t="s">
         <v>34</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="5">
         <v>45658</v>
       </c>
       <c r="C50" t="s">
@@ -3008,7 +3015,7 @@
       <c r="A51" t="s">
         <v>34</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="5">
         <v>45689</v>
       </c>
       <c r="C51" t="s">
@@ -3052,7 +3059,7 @@
       <c r="A52" t="s">
         <v>34</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="5">
         <v>45717</v>
       </c>
       <c r="C52" t="s">
@@ -3096,7 +3103,7 @@
       <c r="A53" t="s">
         <v>34</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="5">
         <v>45748</v>
       </c>
       <c r="C53" t="s">
@@ -3140,7 +3147,7 @@
       <c r="A54" t="s">
         <v>35</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="5">
         <v>45658</v>
       </c>
       <c r="C54" t="s">
@@ -3184,7 +3191,7 @@
       <c r="A55" t="s">
         <v>35</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="5">
         <v>45689</v>
       </c>
       <c r="C55" t="s">
@@ -3228,7 +3235,7 @@
       <c r="A56" t="s">
         <v>35</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="5">
         <v>45717</v>
       </c>
       <c r="C56" t="s">
@@ -3272,7 +3279,7 @@
       <c r="A57" t="s">
         <v>35</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="5">
         <v>45748</v>
       </c>
       <c r="C57" t="s">
@@ -3316,7 +3323,7 @@
       <c r="A58" t="s">
         <v>36</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="5">
         <v>45658</v>
       </c>
       <c r="C58" t="s">
@@ -3360,7 +3367,7 @@
       <c r="A59" t="s">
         <v>36</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="5">
         <v>45689</v>
       </c>
       <c r="C59" t="s">
@@ -3404,7 +3411,7 @@
       <c r="A60" t="s">
         <v>36</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="5">
         <v>45717</v>
       </c>
       <c r="C60" t="s">
@@ -3448,7 +3455,7 @@
       <c r="A61" t="s">
         <v>36</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="5">
         <v>45748</v>
       </c>
       <c r="C61" t="s">
@@ -3492,7 +3499,7 @@
       <c r="A62" t="s">
         <v>37</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="5">
         <v>45658</v>
       </c>
       <c r="C62" t="s">
@@ -3536,7 +3543,7 @@
       <c r="A63" t="s">
         <v>37</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="5">
         <v>45689</v>
       </c>
       <c r="C63" t="s">
@@ -3580,7 +3587,7 @@
       <c r="A64" t="s">
         <v>37</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="5">
         <v>45717</v>
       </c>
       <c r="C64" t="s">
@@ -3624,7 +3631,7 @@
       <c r="A65" t="s">
         <v>37</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="5">
         <v>45748</v>
       </c>
       <c r="C65" t="s">
@@ -3668,7 +3675,7 @@
       <c r="A66" t="s">
         <v>38</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="5">
         <v>45658</v>
       </c>
       <c r="C66" t="s">
@@ -3712,7 +3719,7 @@
       <c r="A67" t="s">
         <v>38</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="5">
         <v>45689</v>
       </c>
       <c r="C67" t="s">
@@ -3756,7 +3763,7 @@
       <c r="A68" t="s">
         <v>38</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="5">
         <v>45717</v>
       </c>
       <c r="C68" t="s">
@@ -3800,7 +3807,7 @@
       <c r="A69" t="s">
         <v>38</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="5">
         <v>45748</v>
       </c>
       <c r="C69" t="s">
@@ -3844,7 +3851,7 @@
       <c r="A70" t="s">
         <v>39</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="5">
         <v>45658</v>
       </c>
       <c r="C70" t="s">
@@ -3888,7 +3895,7 @@
       <c r="A71" t="s">
         <v>39</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="5">
         <v>45689</v>
       </c>
       <c r="C71" t="s">
@@ -3932,7 +3939,7 @@
       <c r="A72" t="s">
         <v>39</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="5">
         <v>45717</v>
       </c>
       <c r="C72" t="s">
@@ -3976,7 +3983,7 @@
       <c r="A73" t="s">
         <v>39</v>
       </c>
-      <c r="B73">
+      <c r="B73" s="5">
         <v>45748</v>
       </c>
       <c r="C73" t="s">
@@ -4017,7 +4024,7 @@
       <c r="A74" t="s">
         <v>40</v>
       </c>
-      <c r="B74">
+      <c r="B74" s="5">
         <v>45658</v>
       </c>
       <c r="C74" t="s">
@@ -4061,7 +4068,7 @@
       <c r="A75" t="s">
         <v>40</v>
       </c>
-      <c r="B75">
+      <c r="B75" s="5">
         <v>45689</v>
       </c>
       <c r="C75" t="s">
@@ -4105,7 +4112,7 @@
       <c r="A76" t="s">
         <v>40</v>
       </c>
-      <c r="B76">
+      <c r="B76" s="5">
         <v>45717</v>
       </c>
       <c r="C76" t="s">
@@ -4149,7 +4156,7 @@
       <c r="A77" t="s">
         <v>40</v>
       </c>
-      <c r="B77">
+      <c r="B77" s="5">
         <v>45748</v>
       </c>
       <c r="C77" t="s">
@@ -4193,7 +4200,7 @@
       <c r="A78" t="s">
         <v>41</v>
       </c>
-      <c r="B78">
+      <c r="B78" s="5">
         <v>45658</v>
       </c>
       <c r="C78" t="s">
@@ -4237,7 +4244,7 @@
       <c r="A79" t="s">
         <v>41</v>
       </c>
-      <c r="B79">
+      <c r="B79" s="5">
         <v>45689</v>
       </c>
       <c r="C79" t="s">
@@ -4281,7 +4288,7 @@
       <c r="A80" t="s">
         <v>41</v>
       </c>
-      <c r="B80">
+      <c r="B80" s="5">
         <v>45717</v>
       </c>
       <c r="C80" t="s">
@@ -4325,7 +4332,7 @@
       <c r="A81" t="s">
         <v>41</v>
       </c>
-      <c r="B81">
+      <c r="B81" s="5">
         <v>45748</v>
       </c>
       <c r="C81" t="s">
@@ -4369,7 +4376,7 @@
       <c r="A82" t="s">
         <v>42</v>
       </c>
-      <c r="B82">
+      <c r="B82" s="5">
         <v>45658</v>
       </c>
       <c r="C82" t="s">
@@ -4413,7 +4420,7 @@
       <c r="A83" t="s">
         <v>42</v>
       </c>
-      <c r="B83">
+      <c r="B83" s="5">
         <v>45689</v>
       </c>
       <c r="C83" t="s">
@@ -4457,7 +4464,7 @@
       <c r="A84" t="s">
         <v>42</v>
       </c>
-      <c r="B84">
+      <c r="B84" s="5">
         <v>45717</v>
       </c>
       <c r="C84" t="s">
@@ -4501,7 +4508,7 @@
       <c r="A85" t="s">
         <v>42</v>
       </c>
-      <c r="B85">
+      <c r="B85" s="5">
         <v>45748</v>
       </c>
       <c r="C85" t="s">
@@ -4545,7 +4552,7 @@
       <c r="A86" t="s">
         <v>43</v>
       </c>
-      <c r="B86">
+      <c r="B86" s="5">
         <v>45658</v>
       </c>
       <c r="C86" t="s">
@@ -4589,7 +4596,7 @@
       <c r="A87" t="s">
         <v>43</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="5">
         <v>45689</v>
       </c>
       <c r="C87" t="s">
@@ -4630,7 +4637,7 @@
       <c r="A88" t="s">
         <v>43</v>
       </c>
-      <c r="B88">
+      <c r="B88" s="5">
         <v>45717</v>
       </c>
       <c r="C88" t="s">
@@ -4674,7 +4681,7 @@
       <c r="A89" t="s">
         <v>43</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="5">
         <v>45748</v>
       </c>
       <c r="C89" t="s">
@@ -4718,7 +4725,7 @@
       <c r="A90" t="s">
         <v>44</v>
       </c>
-      <c r="B90">
+      <c r="B90" s="5">
         <v>45658</v>
       </c>
       <c r="C90" t="s">
@@ -4762,7 +4769,7 @@
       <c r="A91" t="s">
         <v>44</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="5">
         <v>45689</v>
       </c>
       <c r="C91" t="s">
@@ -4806,7 +4813,7 @@
       <c r="A92" t="s">
         <v>44</v>
       </c>
-      <c r="B92">
+      <c r="B92" s="5">
         <v>45717</v>
       </c>
       <c r="C92" t="s">
@@ -4850,7 +4857,7 @@
       <c r="A93" t="s">
         <v>44</v>
       </c>
-      <c r="B93">
+      <c r="B93" s="5">
         <v>45748</v>
       </c>
       <c r="C93" t="s">
@@ -4894,7 +4901,7 @@
       <c r="A94" t="s">
         <v>45</v>
       </c>
-      <c r="B94">
+      <c r="B94" s="5">
         <v>45658</v>
       </c>
       <c r="C94" t="s">
@@ -4938,7 +4945,7 @@
       <c r="A95" t="s">
         <v>45</v>
       </c>
-      <c r="B95">
+      <c r="B95" s="5">
         <v>45689</v>
       </c>
       <c r="C95" t="s">
@@ -4982,7 +4989,7 @@
       <c r="A96" t="s">
         <v>45</v>
       </c>
-      <c r="B96">
+      <c r="B96" s="5">
         <v>45717</v>
       </c>
       <c r="C96" t="s">
@@ -5026,7 +5033,7 @@
       <c r="A97" t="s">
         <v>45</v>
       </c>
-      <c r="B97">
+      <c r="B97" s="5">
         <v>45748</v>
       </c>
       <c r="C97" t="s">
@@ -5070,7 +5077,7 @@
       <c r="A98" t="s">
         <v>46</v>
       </c>
-      <c r="B98">
+      <c r="B98" s="5">
         <v>45658</v>
       </c>
       <c r="C98" t="s">
@@ -5114,7 +5121,7 @@
       <c r="A99" t="s">
         <v>46</v>
       </c>
-      <c r="B99">
+      <c r="B99" s="5">
         <v>45689</v>
       </c>
       <c r="C99" t="s">
@@ -5158,7 +5165,7 @@
       <c r="A100" t="s">
         <v>46</v>
       </c>
-      <c r="B100">
+      <c r="B100" s="5">
         <v>45717</v>
       </c>
       <c r="C100" t="s">
@@ -5199,7 +5206,7 @@
       <c r="A101" t="s">
         <v>46</v>
       </c>
-      <c r="B101">
+      <c r="B101" s="5">
         <v>45748</v>
       </c>
       <c r="C101" t="s">
@@ -5243,7 +5250,7 @@
       <c r="A102" t="s">
         <v>47</v>
       </c>
-      <c r="B102">
+      <c r="B102" s="5">
         <v>45658</v>
       </c>
       <c r="C102" t="s">
@@ -5287,7 +5294,7 @@
       <c r="A103" t="s">
         <v>47</v>
       </c>
-      <c r="B103">
+      <c r="B103" s="5">
         <v>45689</v>
       </c>
       <c r="C103" t="s">
@@ -5331,7 +5338,7 @@
       <c r="A104" t="s">
         <v>47</v>
       </c>
-      <c r="B104">
+      <c r="B104" s="5">
         <v>45717</v>
       </c>
       <c r="C104" t="s">
@@ -5375,7 +5382,7 @@
       <c r="A105" t="s">
         <v>47</v>
       </c>
-      <c r="B105">
+      <c r="B105" s="5">
         <v>45748</v>
       </c>
       <c r="C105" t="s">
@@ -5419,7 +5426,7 @@
       <c r="A106" t="s">
         <v>48</v>
       </c>
-      <c r="B106">
+      <c r="B106" s="5">
         <v>45658</v>
       </c>
       <c r="C106" t="s">
@@ -5463,7 +5470,7 @@
       <c r="A107" t="s">
         <v>48</v>
       </c>
-      <c r="B107">
+      <c r="B107" s="5">
         <v>45689</v>
       </c>
       <c r="C107" t="s">
@@ -5507,7 +5514,7 @@
       <c r="A108" t="s">
         <v>48</v>
       </c>
-      <c r="B108">
+      <c r="B108" s="5">
         <v>45717</v>
       </c>
       <c r="C108" t="s">
@@ -5551,7 +5558,7 @@
       <c r="A109" t="s">
         <v>48</v>
       </c>
-      <c r="B109">
+      <c r="B109" s="5">
         <v>45748</v>
       </c>
       <c r="C109" t="s">
@@ -5595,7 +5602,7 @@
       <c r="A110" t="s">
         <v>49</v>
       </c>
-      <c r="B110">
+      <c r="B110" s="5">
         <v>45658</v>
       </c>
       <c r="C110" t="s">
@@ -5639,7 +5646,7 @@
       <c r="A111" t="s">
         <v>49</v>
       </c>
-      <c r="B111">
+      <c r="B111" s="5">
         <v>45689</v>
       </c>
       <c r="C111" t="s">
@@ -5683,7 +5690,7 @@
       <c r="A112" t="s">
         <v>49</v>
       </c>
-      <c r="B112">
+      <c r="B112" s="5">
         <v>45717</v>
       </c>
       <c r="C112" t="s">
@@ -5727,7 +5734,7 @@
       <c r="A113" t="s">
         <v>49</v>
       </c>
-      <c r="B113">
+      <c r="B113" s="5">
         <v>45748</v>
       </c>
       <c r="C113" t="s">
@@ -5771,7 +5778,7 @@
       <c r="A114" t="s">
         <v>50</v>
       </c>
-      <c r="B114">
+      <c r="B114" s="5">
         <v>45658</v>
       </c>
       <c r="C114" t="s">
@@ -5815,7 +5822,7 @@
       <c r="A115" t="s">
         <v>50</v>
       </c>
-      <c r="B115">
+      <c r="B115" s="5">
         <v>45689</v>
       </c>
       <c r="C115" t="s">
@@ -5859,7 +5866,7 @@
       <c r="A116" t="s">
         <v>50</v>
       </c>
-      <c r="B116">
+      <c r="B116" s="5">
         <v>45717</v>
       </c>
       <c r="C116" t="s">
@@ -5903,7 +5910,7 @@
       <c r="A117" t="s">
         <v>50</v>
       </c>
-      <c r="B117">
+      <c r="B117" s="5">
         <v>45748</v>
       </c>
       <c r="C117" t="s">
@@ -5947,7 +5954,7 @@
       <c r="A118" t="s">
         <v>51</v>
       </c>
-      <c r="B118">
+      <c r="B118" s="5">
         <v>45658</v>
       </c>
       <c r="C118" t="s">
@@ -5991,7 +5998,7 @@
       <c r="A119" t="s">
         <v>51</v>
       </c>
-      <c r="B119">
+      <c r="B119" s="5">
         <v>45689</v>
       </c>
       <c r="C119" t="s">
@@ -6035,7 +6042,7 @@
       <c r="A120" t="s">
         <v>51</v>
       </c>
-      <c r="B120">
+      <c r="B120" s="5">
         <v>45717</v>
       </c>
       <c r="C120" t="s">
@@ -6079,7 +6086,7 @@
       <c r="A121" t="s">
         <v>51</v>
       </c>
-      <c r="B121">
+      <c r="B121" s="5">
         <v>45748</v>
       </c>
       <c r="C121" t="s">
@@ -6123,7 +6130,7 @@
       <c r="A122" t="s">
         <v>52</v>
       </c>
-      <c r="B122">
+      <c r="B122" s="5">
         <v>45658</v>
       </c>
       <c r="C122" t="s">
@@ -6167,7 +6174,7 @@
       <c r="A123" t="s">
         <v>52</v>
       </c>
-      <c r="B123">
+      <c r="B123" s="5">
         <v>45689</v>
       </c>
       <c r="C123" t="s">
@@ -6211,7 +6218,7 @@
       <c r="A124" t="s">
         <v>52</v>
       </c>
-      <c r="B124">
+      <c r="B124" s="5">
         <v>45717</v>
       </c>
       <c r="C124" t="s">
@@ -6255,7 +6262,7 @@
       <c r="A125" t="s">
         <v>52</v>
       </c>
-      <c r="B125">
+      <c r="B125" s="5">
         <v>45748</v>
       </c>
       <c r="C125" t="s">
@@ -6299,7 +6306,7 @@
       <c r="A126" t="s">
         <v>53</v>
       </c>
-      <c r="B126">
+      <c r="B126" s="5">
         <v>45658</v>
       </c>
       <c r="C126" t="s">
@@ -6343,7 +6350,7 @@
       <c r="A127" t="s">
         <v>53</v>
       </c>
-      <c r="B127">
+      <c r="B127" s="5">
         <v>45689</v>
       </c>
       <c r="C127" t="s">
@@ -6387,7 +6394,7 @@
       <c r="A128" t="s">
         <v>53</v>
       </c>
-      <c r="B128">
+      <c r="B128" s="5">
         <v>45717</v>
       </c>
       <c r="C128" t="s">
@@ -6431,7 +6438,7 @@
       <c r="A129" t="s">
         <v>53</v>
       </c>
-      <c r="B129">
+      <c r="B129" s="5">
         <v>45748</v>
       </c>
       <c r="C129" t="s">
@@ -6475,7 +6482,7 @@
       <c r="A130" t="s">
         <v>54</v>
       </c>
-      <c r="B130">
+      <c r="B130" s="5">
         <v>45658</v>
       </c>
       <c r="C130" t="s">
@@ -6519,7 +6526,7 @@
       <c r="A131" t="s">
         <v>54</v>
       </c>
-      <c r="B131">
+      <c r="B131" s="5">
         <v>45689</v>
       </c>
       <c r="C131" t="s">
@@ -6563,7 +6570,7 @@
       <c r="A132" t="s">
         <v>54</v>
       </c>
-      <c r="B132">
+      <c r="B132" s="5">
         <v>45717</v>
       </c>
       <c r="C132" t="s">
@@ -6607,7 +6614,7 @@
       <c r="A133" t="s">
         <v>54</v>
       </c>
-      <c r="B133">
+      <c r="B133" s="5">
         <v>45748</v>
       </c>
       <c r="C133" t="s">
@@ -6651,7 +6658,7 @@
       <c r="A134" t="s">
         <v>55</v>
       </c>
-      <c r="B134">
+      <c r="B134" s="5">
         <v>45658</v>
       </c>
       <c r="C134" t="s">
@@ -6695,7 +6702,7 @@
       <c r="A135" t="s">
         <v>55</v>
       </c>
-      <c r="B135">
+      <c r="B135" s="5">
         <v>45689</v>
       </c>
       <c r="C135" t="s">
@@ -6736,7 +6743,7 @@
       <c r="A136" t="s">
         <v>55</v>
       </c>
-      <c r="B136">
+      <c r="B136" s="5">
         <v>45717</v>
       </c>
       <c r="C136" t="s">
@@ -6780,7 +6787,7 @@
       <c r="A137" t="s">
         <v>55</v>
       </c>
-      <c r="B137">
+      <c r="B137" s="5">
         <v>45748</v>
       </c>
       <c r="C137" t="s">
@@ -6824,7 +6831,7 @@
       <c r="A138" t="s">
         <v>56</v>
       </c>
-      <c r="B138">
+      <c r="B138" s="5">
         <v>45658</v>
       </c>
       <c r="C138" t="s">
@@ -6865,7 +6872,7 @@
       <c r="A139" t="s">
         <v>56</v>
       </c>
-      <c r="B139">
+      <c r="B139" s="5">
         <v>45689</v>
       </c>
       <c r="C139" t="s">
@@ -6909,7 +6916,7 @@
       <c r="A140" t="s">
         <v>56</v>
       </c>
-      <c r="B140">
+      <c r="B140" s="5">
         <v>45717</v>
       </c>
       <c r="C140" t="s">
@@ -6953,7 +6960,7 @@
       <c r="A141" t="s">
         <v>56</v>
       </c>
-      <c r="B141">
+      <c r="B141" s="5">
         <v>45748</v>
       </c>
       <c r="C141" t="s">
@@ -6997,7 +7004,7 @@
       <c r="A142" t="s">
         <v>57</v>
       </c>
-      <c r="B142">
+      <c r="B142" s="5">
         <v>45658</v>
       </c>
       <c r="C142" t="s">
@@ -7041,7 +7048,7 @@
       <c r="A143" t="s">
         <v>57</v>
       </c>
-      <c r="B143">
+      <c r="B143" s="5">
         <v>45689</v>
       </c>
       <c r="C143" t="s">
@@ -7085,7 +7092,7 @@
       <c r="A144" t="s">
         <v>57</v>
       </c>
-      <c r="B144">
+      <c r="B144" s="5">
         <v>45717</v>
       </c>
       <c r="C144" t="s">
@@ -7129,7 +7136,7 @@
       <c r="A145" t="s">
         <v>57</v>
       </c>
-      <c r="B145">
+      <c r="B145" s="5">
         <v>45748</v>
       </c>
       <c r="C145" t="s">
@@ -7173,7 +7180,7 @@
       <c r="A146" t="s">
         <v>58</v>
       </c>
-      <c r="B146">
+      <c r="B146" s="5">
         <v>45658</v>
       </c>
       <c r="C146" t="s">
@@ -7217,7 +7224,7 @@
       <c r="A147" t="s">
         <v>58</v>
       </c>
-      <c r="B147">
+      <c r="B147" s="5">
         <v>45689</v>
       </c>
       <c r="C147" t="s">
@@ -7261,7 +7268,7 @@
       <c r="A148" t="s">
         <v>58</v>
       </c>
-      <c r="B148">
+      <c r="B148" s="5">
         <v>45717</v>
       </c>
       <c r="C148" t="s">
@@ -7305,7 +7312,7 @@
       <c r="A149" t="s">
         <v>58</v>
       </c>
-      <c r="B149">
+      <c r="B149" s="5">
         <v>45748</v>
       </c>
       <c r="C149" t="s">
@@ -7349,7 +7356,7 @@
       <c r="A150" t="s">
         <v>59</v>
       </c>
-      <c r="B150">
+      <c r="B150" s="5">
         <v>45658</v>
       </c>
       <c r="C150" t="s">
@@ -7393,7 +7400,7 @@
       <c r="A151" t="s">
         <v>59</v>
       </c>
-      <c r="B151">
+      <c r="B151" s="5">
         <v>45689</v>
       </c>
       <c r="C151" t="s">
@@ -7437,7 +7444,7 @@
       <c r="A152" t="s">
         <v>59</v>
       </c>
-      <c r="B152">
+      <c r="B152" s="5">
         <v>45717</v>
       </c>
       <c r="C152" t="s">
@@ -7481,7 +7488,7 @@
       <c r="A153" t="s">
         <v>59</v>
       </c>
-      <c r="B153">
+      <c r="B153" s="5">
         <v>45748</v>
       </c>
       <c r="C153" t="s">
@@ -7525,7 +7532,7 @@
       <c r="A154" t="s">
         <v>60</v>
       </c>
-      <c r="B154">
+      <c r="B154" s="5">
         <v>45658</v>
       </c>
       <c r="C154" t="s">
@@ -7569,7 +7576,7 @@
       <c r="A155" t="s">
         <v>60</v>
       </c>
-      <c r="B155">
+      <c r="B155" s="5">
         <v>45689</v>
       </c>
       <c r="C155" t="s">
@@ -7613,7 +7620,7 @@
       <c r="A156" t="s">
         <v>60</v>
       </c>
-      <c r="B156">
+      <c r="B156" s="5">
         <v>45717</v>
       </c>
       <c r="C156" t="s">
@@ -7657,7 +7664,7 @@
       <c r="A157" t="s">
         <v>60</v>
       </c>
-      <c r="B157">
+      <c r="B157" s="5">
         <v>45748</v>
       </c>
       <c r="C157" t="s">
@@ -7701,7 +7708,7 @@
       <c r="A158" t="s">
         <v>61</v>
       </c>
-      <c r="B158">
+      <c r="B158" s="5">
         <v>45658</v>
       </c>
       <c r="C158" t="s">
@@ -7745,7 +7752,7 @@
       <c r="A159" t="s">
         <v>61</v>
       </c>
-      <c r="B159">
+      <c r="B159" s="5">
         <v>45689</v>
       </c>
       <c r="C159" t="s">
@@ -7789,7 +7796,7 @@
       <c r="A160" t="s">
         <v>61</v>
       </c>
-      <c r="B160">
+      <c r="B160" s="5">
         <v>45717</v>
       </c>
       <c r="C160" t="s">
@@ -7833,7 +7840,7 @@
       <c r="A161" t="s">
         <v>61</v>
       </c>
-      <c r="B161">
+      <c r="B161" s="5">
         <v>45748</v>
       </c>
       <c r="C161" t="s">
@@ -7877,7 +7884,7 @@
       <c r="A162" t="s">
         <v>62</v>
       </c>
-      <c r="B162">
+      <c r="B162" s="5">
         <v>45658</v>
       </c>
       <c r="C162" t="s">
@@ -7921,7 +7928,7 @@
       <c r="A163" t="s">
         <v>62</v>
       </c>
-      <c r="B163">
+      <c r="B163" s="5">
         <v>45689</v>
       </c>
       <c r="C163" t="s">
@@ -7965,7 +7972,7 @@
       <c r="A164" t="s">
         <v>62</v>
       </c>
-      <c r="B164">
+      <c r="B164" s="5">
         <v>45717</v>
       </c>
       <c r="C164" t="s">
@@ -8006,7 +8013,7 @@
       <c r="A165" t="s">
         <v>62</v>
       </c>
-      <c r="B165">
+      <c r="B165" s="5">
         <v>45748</v>
       </c>
       <c r="C165" t="s">
@@ -8050,7 +8057,7 @@
       <c r="A166" t="s">
         <v>63</v>
       </c>
-      <c r="B166">
+      <c r="B166" s="5">
         <v>45658</v>
       </c>
       <c r="C166" t="s">
@@ -8094,7 +8101,7 @@
       <c r="A167" t="s">
         <v>63</v>
       </c>
-      <c r="B167">
+      <c r="B167" s="5">
         <v>45689</v>
       </c>
       <c r="C167" t="s">
@@ -8138,7 +8145,7 @@
       <c r="A168" t="s">
         <v>63</v>
       </c>
-      <c r="B168">
+      <c r="B168" s="5">
         <v>45717</v>
       </c>
       <c r="C168" t="s">
@@ -8182,7 +8189,7 @@
       <c r="A169" t="s">
         <v>63</v>
       </c>
-      <c r="B169">
+      <c r="B169" s="5">
         <v>45748</v>
       </c>
       <c r="C169" t="s">
@@ -8226,7 +8233,7 @@
       <c r="A170" t="s">
         <v>64</v>
       </c>
-      <c r="B170">
+      <c r="B170" s="5">
         <v>45658</v>
       </c>
       <c r="C170" t="s">
@@ -8270,7 +8277,7 @@
       <c r="A171" t="s">
         <v>64</v>
       </c>
-      <c r="B171">
+      <c r="B171" s="5">
         <v>45689</v>
       </c>
       <c r="C171" t="s">
@@ -8314,7 +8321,7 @@
       <c r="A172" t="s">
         <v>64</v>
       </c>
-      <c r="B172">
+      <c r="B172" s="5">
         <v>45717</v>
       </c>
       <c r="C172" t="s">
@@ -8358,7 +8365,7 @@
       <c r="A173" t="s">
         <v>64</v>
       </c>
-      <c r="B173">
+      <c r="B173" s="5">
         <v>45748</v>
       </c>
       <c r="C173" t="s">
@@ -8402,7 +8409,7 @@
       <c r="A174" t="s">
         <v>65</v>
       </c>
-      <c r="B174">
+      <c r="B174" s="5">
         <v>45658</v>
       </c>
       <c r="C174" t="s">
@@ -8446,7 +8453,7 @@
       <c r="A175" t="s">
         <v>65</v>
       </c>
-      <c r="B175">
+      <c r="B175" s="5">
         <v>45689</v>
       </c>
       <c r="C175" t="s">
@@ -8490,7 +8497,7 @@
       <c r="A176" t="s">
         <v>65</v>
       </c>
-      <c r="B176">
+      <c r="B176" s="5">
         <v>45717</v>
       </c>
       <c r="C176" t="s">
@@ -8534,7 +8541,7 @@
       <c r="A177" t="s">
         <v>65</v>
       </c>
-      <c r="B177">
+      <c r="B177" s="5">
         <v>45748</v>
       </c>
       <c r="C177" t="s">
@@ -8578,7 +8585,7 @@
       <c r="A178" t="s">
         <v>66</v>
       </c>
-      <c r="B178">
+      <c r="B178" s="5">
         <v>45658</v>
       </c>
       <c r="C178" t="s">
@@ -8622,7 +8629,7 @@
       <c r="A179" t="s">
         <v>66</v>
       </c>
-      <c r="B179">
+      <c r="B179" s="5">
         <v>45689</v>
       </c>
       <c r="C179" t="s">
@@ -8666,7 +8673,7 @@
       <c r="A180" t="s">
         <v>66</v>
       </c>
-      <c r="B180">
+      <c r="B180" s="5">
         <v>45717</v>
       </c>
       <c r="C180" t="s">
@@ -8710,7 +8717,7 @@
       <c r="A181" t="s">
         <v>66</v>
       </c>
-      <c r="B181">
+      <c r="B181" s="5">
         <v>45748</v>
       </c>
       <c r="C181" t="s">
@@ -8754,7 +8761,7 @@
       <c r="A182" t="s">
         <v>67</v>
       </c>
-      <c r="B182">
+      <c r="B182" s="5">
         <v>45658</v>
       </c>
       <c r="C182" t="s">
@@ -8798,7 +8805,7 @@
       <c r="A183" t="s">
         <v>67</v>
       </c>
-      <c r="B183">
+      <c r="B183" s="5">
         <v>45689</v>
       </c>
       <c r="C183" t="s">
@@ -8842,7 +8849,7 @@
       <c r="A184" t="s">
         <v>67</v>
       </c>
-      <c r="B184">
+      <c r="B184" s="5">
         <v>45717</v>
       </c>
       <c r="C184" t="s">
@@ -8886,7 +8893,7 @@
       <c r="A185" t="s">
         <v>67</v>
       </c>
-      <c r="B185">
+      <c r="B185" s="5">
         <v>45748</v>
       </c>
       <c r="C185" t="s">
@@ -8930,7 +8937,7 @@
       <c r="A186" t="s">
         <v>68</v>
       </c>
-      <c r="B186">
+      <c r="B186" s="5">
         <v>45658</v>
       </c>
       <c r="C186" t="s">
@@ -8974,7 +8981,7 @@
       <c r="A187" t="s">
         <v>68</v>
       </c>
-      <c r="B187">
+      <c r="B187" s="5">
         <v>45689</v>
       </c>
       <c r="C187" t="s">
@@ -9018,7 +9025,7 @@
       <c r="A188" t="s">
         <v>68</v>
       </c>
-      <c r="B188">
+      <c r="B188" s="5">
         <v>45717</v>
       </c>
       <c r="C188" t="s">
@@ -9062,7 +9069,7 @@
       <c r="A189" t="s">
         <v>68</v>
       </c>
-      <c r="B189">
+      <c r="B189" s="5">
         <v>45748</v>
       </c>
       <c r="C189" t="s">
@@ -9106,7 +9113,7 @@
       <c r="A190" t="s">
         <v>69</v>
       </c>
-      <c r="B190">
+      <c r="B190" s="5">
         <v>45658</v>
       </c>
       <c r="C190" t="s">
@@ -9150,7 +9157,7 @@
       <c r="A191" t="s">
         <v>69</v>
       </c>
-      <c r="B191">
+      <c r="B191" s="5">
         <v>45689</v>
       </c>
       <c r="C191" t="s">
@@ -9194,7 +9201,7 @@
       <c r="A192" t="s">
         <v>69</v>
       </c>
-      <c r="B192">
+      <c r="B192" s="5">
         <v>45717</v>
       </c>
       <c r="C192" t="s">
@@ -9238,7 +9245,7 @@
       <c r="A193" t="s">
         <v>69</v>
       </c>
-      <c r="B193">
+      <c r="B193" s="5">
         <v>45748</v>
       </c>
       <c r="C193" t="s">
@@ -9282,7 +9289,7 @@
       <c r="A194" t="s">
         <v>70</v>
       </c>
-      <c r="B194">
+      <c r="B194" s="5">
         <v>45658</v>
       </c>
       <c r="C194" t="s">
@@ -9326,7 +9333,7 @@
       <c r="A195" t="s">
         <v>70</v>
       </c>
-      <c r="B195">
+      <c r="B195" s="5">
         <v>45689</v>
       </c>
       <c r="C195" t="s">
@@ -9370,7 +9377,7 @@
       <c r="A196" t="s">
         <v>70</v>
       </c>
-      <c r="B196">
+      <c r="B196" s="5">
         <v>45717</v>
       </c>
       <c r="C196" t="s">
@@ -9414,7 +9421,7 @@
       <c r="A197" t="s">
         <v>70</v>
       </c>
-      <c r="B197">
+      <c r="B197" s="5">
         <v>45748</v>
       </c>
       <c r="C197" t="s">
@@ -9455,7 +9462,7 @@
       <c r="A198" t="s">
         <v>71</v>
       </c>
-      <c r="B198">
+      <c r="B198" s="5">
         <v>45658</v>
       </c>
       <c r="C198" t="s">
@@ -9499,7 +9506,7 @@
       <c r="A199" t="s">
         <v>71</v>
       </c>
-      <c r="B199">
+      <c r="B199" s="5">
         <v>45689</v>
       </c>
       <c r="C199" t="s">
@@ -9543,7 +9550,7 @@
       <c r="A200" t="s">
         <v>71</v>
       </c>
-      <c r="B200">
+      <c r="B200" s="5">
         <v>45717</v>
       </c>
       <c r="C200" t="s">
@@ -9587,7 +9594,7 @@
       <c r="A201" t="s">
         <v>71</v>
       </c>
-      <c r="B201">
+      <c r="B201" s="5">
         <v>45748</v>
       </c>
       <c r="C201" t="s">
@@ -9631,7 +9638,7 @@
       <c r="A202" t="s">
         <v>72</v>
       </c>
-      <c r="B202">
+      <c r="B202" s="5">
         <v>45658</v>
       </c>
       <c r="C202" t="s">
@@ -9675,7 +9682,7 @@
       <c r="A203" t="s">
         <v>72</v>
       </c>
-      <c r="B203">
+      <c r="B203" s="5">
         <v>45689</v>
       </c>
       <c r="C203" t="s">
@@ -9719,7 +9726,7 @@
       <c r="A204" t="s">
         <v>72</v>
       </c>
-      <c r="B204">
+      <c r="B204" s="5">
         <v>45717</v>
       </c>
       <c r="C204" t="s">
@@ -9763,7 +9770,7 @@
       <c r="A205" t="s">
         <v>72</v>
       </c>
-      <c r="B205">
+      <c r="B205" s="5">
         <v>45748</v>
       </c>
       <c r="C205" t="s">
@@ -9807,7 +9814,7 @@
       <c r="A206" t="s">
         <v>73</v>
       </c>
-      <c r="B206">
+      <c r="B206" s="5">
         <v>45658</v>
       </c>
       <c r="C206" t="s">
@@ -9851,7 +9858,7 @@
       <c r="A207" t="s">
         <v>73</v>
       </c>
-      <c r="B207">
+      <c r="B207" s="5">
         <v>45689</v>
       </c>
       <c r="C207" t="s">
@@ -9895,7 +9902,7 @@
       <c r="A208" t="s">
         <v>73</v>
       </c>
-      <c r="B208">
+      <c r="B208" s="5">
         <v>45717</v>
       </c>
       <c r="C208" t="s">
@@ -9939,7 +9946,7 @@
       <c r="A209" t="s">
         <v>73</v>
       </c>
-      <c r="B209">
+      <c r="B209" s="5">
         <v>45748</v>
       </c>
       <c r="C209" t="s">
@@ -9983,7 +9990,7 @@
       <c r="A210" t="s">
         <v>74</v>
       </c>
-      <c r="B210">
+      <c r="B210" s="5">
         <v>45658</v>
       </c>
       <c r="C210" t="s">
@@ -10027,7 +10034,7 @@
       <c r="A211" t="s">
         <v>74</v>
       </c>
-      <c r="B211">
+      <c r="B211" s="5">
         <v>45689</v>
       </c>
       <c r="C211" t="s">
@@ -10071,7 +10078,7 @@
       <c r="A212" t="s">
         <v>74</v>
       </c>
-      <c r="B212">
+      <c r="B212" s="5">
         <v>45717</v>
       </c>
       <c r="C212" t="s">
@@ -10115,7 +10122,7 @@
       <c r="A213" t="s">
         <v>74</v>
       </c>
-      <c r="B213">
+      <c r="B213" s="5">
         <v>45748</v>
       </c>
       <c r="C213" t="s">
@@ -10159,7 +10166,7 @@
       <c r="A214" t="s">
         <v>75</v>
       </c>
-      <c r="B214">
+      <c r="B214" s="5">
         <v>45658</v>
       </c>
       <c r="C214" t="s">
@@ -10203,7 +10210,7 @@
       <c r="A215" t="s">
         <v>75</v>
       </c>
-      <c r="B215">
+      <c r="B215" s="5">
         <v>45689</v>
       </c>
       <c r="C215" t="s">
@@ -10247,7 +10254,7 @@
       <c r="A216" t="s">
         <v>75</v>
       </c>
-      <c r="B216">
+      <c r="B216" s="5">
         <v>45717</v>
       </c>
       <c r="C216" t="s">
@@ -10291,7 +10298,7 @@
       <c r="A217" t="s">
         <v>75</v>
       </c>
-      <c r="B217">
+      <c r="B217" s="5">
         <v>45748</v>
       </c>
       <c r="C217" t="s">
@@ -10335,7 +10342,7 @@
       <c r="A218" t="s">
         <v>76</v>
       </c>
-      <c r="B218">
+      <c r="B218" s="5">
         <v>45658</v>
       </c>
       <c r="C218" t="s">
@@ -10379,7 +10386,7 @@
       <c r="A219" t="s">
         <v>76</v>
       </c>
-      <c r="B219">
+      <c r="B219" s="5">
         <v>45689</v>
       </c>
       <c r="C219" t="s">
@@ -10423,7 +10430,7 @@
       <c r="A220" t="s">
         <v>76</v>
       </c>
-      <c r="B220">
+      <c r="B220" s="5">
         <v>45717</v>
       </c>
       <c r="C220" t="s">
@@ -10467,7 +10474,7 @@
       <c r="A221" t="s">
         <v>76</v>
       </c>
-      <c r="B221">
+      <c r="B221" s="5">
         <v>45748</v>
       </c>
       <c r="C221" t="s">
@@ -10511,7 +10518,7 @@
       <c r="A222" t="s">
         <v>77</v>
       </c>
-      <c r="B222">
+      <c r="B222" s="5">
         <v>45658</v>
       </c>
       <c r="C222" t="s">
@@ -10555,7 +10562,7 @@
       <c r="A223" t="s">
         <v>77</v>
       </c>
-      <c r="B223">
+      <c r="B223" s="5">
         <v>45689</v>
       </c>
       <c r="C223" t="s">
@@ -10599,7 +10606,7 @@
       <c r="A224" t="s">
         <v>77</v>
       </c>
-      <c r="B224">
+      <c r="B224" s="5">
         <v>45717</v>
       </c>
       <c r="C224" t="s">
@@ -10643,7 +10650,7 @@
       <c r="A225" t="s">
         <v>77</v>
       </c>
-      <c r="B225">
+      <c r="B225" s="5">
         <v>45748</v>
       </c>
       <c r="C225" t="s">
@@ -10687,7 +10694,7 @@
       <c r="A226" t="s">
         <v>78</v>
       </c>
-      <c r="B226">
+      <c r="B226" s="5">
         <v>45658</v>
       </c>
       <c r="C226" t="s">
@@ -10731,7 +10738,7 @@
       <c r="A227" t="s">
         <v>78</v>
       </c>
-      <c r="B227">
+      <c r="B227" s="5">
         <v>45689</v>
       </c>
       <c r="C227" t="s">
@@ -10775,7 +10782,7 @@
       <c r="A228" t="s">
         <v>78</v>
       </c>
-      <c r="B228">
+      <c r="B228" s="5">
         <v>45717</v>
       </c>
       <c r="C228" t="s">
@@ -10819,7 +10826,7 @@
       <c r="A229" t="s">
         <v>78</v>
       </c>
-      <c r="B229">
+      <c r="B229" s="5">
         <v>45748</v>
       </c>
       <c r="C229" t="s">
@@ -10860,7 +10867,7 @@
       <c r="A230" t="s">
         <v>79</v>
       </c>
-      <c r="B230">
+      <c r="B230" s="5">
         <v>45658</v>
       </c>
       <c r="C230" t="s">
@@ -10904,7 +10911,7 @@
       <c r="A231" t="s">
         <v>79</v>
       </c>
-      <c r="B231">
+      <c r="B231" s="5">
         <v>45689</v>
       </c>
       <c r="C231" t="s">
@@ -10948,7 +10955,7 @@
       <c r="A232" t="s">
         <v>79</v>
       </c>
-      <c r="B232">
+      <c r="B232" s="5">
         <v>45717</v>
       </c>
       <c r="C232" t="s">
@@ -10992,7 +10999,7 @@
       <c r="A233" t="s">
         <v>79</v>
       </c>
-      <c r="B233">
+      <c r="B233" s="5">
         <v>45748</v>
       </c>
       <c r="C233" t="s">
@@ -11033,7 +11040,7 @@
       <c r="A234" t="s">
         <v>80</v>
       </c>
-      <c r="B234">
+      <c r="B234" s="5">
         <v>45658</v>
       </c>
       <c r="C234" t="s">
@@ -11077,7 +11084,7 @@
       <c r="A235" t="s">
         <v>80</v>
       </c>
-      <c r="B235">
+      <c r="B235" s="5">
         <v>45689</v>
       </c>
       <c r="C235" t="s">
@@ -11121,7 +11128,7 @@
       <c r="A236" t="s">
         <v>80</v>
       </c>
-      <c r="B236">
+      <c r="B236" s="5">
         <v>45717</v>
       </c>
       <c r="C236" t="s">
@@ -11165,7 +11172,7 @@
       <c r="A237" t="s">
         <v>80</v>
       </c>
-      <c r="B237">
+      <c r="B237" s="5">
         <v>45748</v>
       </c>
       <c r="C237" t="s">
@@ -11209,7 +11216,7 @@
       <c r="A238" t="s">
         <v>81</v>
       </c>
-      <c r="B238">
+      <c r="B238" s="5">
         <v>45658</v>
       </c>
       <c r="C238" t="s">
@@ -11253,7 +11260,7 @@
       <c r="A239" t="s">
         <v>81</v>
       </c>
-      <c r="B239">
+      <c r="B239" s="5">
         <v>45689</v>
       </c>
       <c r="C239" t="s">
@@ -11297,7 +11304,7 @@
       <c r="A240" t="s">
         <v>81</v>
       </c>
-      <c r="B240">
+      <c r="B240" s="5">
         <v>45717</v>
       </c>
       <c r="C240" t="s">
@@ -11341,7 +11348,7 @@
       <c r="A241" t="s">
         <v>81</v>
       </c>
-      <c r="B241">
+      <c r="B241" s="5">
         <v>45748</v>
       </c>
       <c r="C241" t="s">
@@ -11385,7 +11392,7 @@
       <c r="A242" t="s">
         <v>82</v>
       </c>
-      <c r="B242">
+      <c r="B242" s="5">
         <v>45658</v>
       </c>
       <c r="C242" t="s">
@@ -11429,7 +11436,7 @@
       <c r="A243" t="s">
         <v>82</v>
       </c>
-      <c r="B243">
+      <c r="B243" s="5">
         <v>45689</v>
       </c>
       <c r="C243" t="s">
@@ -11473,7 +11480,7 @@
       <c r="A244" t="s">
         <v>82</v>
       </c>
-      <c r="B244">
+      <c r="B244" s="5">
         <v>45717</v>
       </c>
       <c r="C244" t="s">
@@ -11517,7 +11524,7 @@
       <c r="A245" t="s">
         <v>82</v>
       </c>
-      <c r="B245">
+      <c r="B245" s="5">
         <v>45748</v>
       </c>
       <c r="C245" t="s">
@@ -11561,7 +11568,7 @@
       <c r="A246" t="s">
         <v>83</v>
       </c>
-      <c r="B246">
+      <c r="B246" s="5">
         <v>45658</v>
       </c>
       <c r="C246" t="s">
@@ -11605,7 +11612,7 @@
       <c r="A247" t="s">
         <v>83</v>
       </c>
-      <c r="B247">
+      <c r="B247" s="5">
         <v>45689</v>
       </c>
       <c r="C247" t="s">
@@ -11649,7 +11656,7 @@
       <c r="A248" t="s">
         <v>83</v>
       </c>
-      <c r="B248">
+      <c r="B248" s="5">
         <v>45717</v>
       </c>
       <c r="C248" t="s">
@@ -11693,7 +11700,7 @@
       <c r="A249" t="s">
         <v>83</v>
       </c>
-      <c r="B249">
+      <c r="B249" s="5">
         <v>45748</v>
       </c>
       <c r="C249" t="s">
@@ -11737,7 +11744,7 @@
       <c r="A250" t="s">
         <v>84</v>
       </c>
-      <c r="B250">
+      <c r="B250" s="5">
         <v>45658</v>
       </c>
       <c r="C250" t="s">
@@ -11778,7 +11785,7 @@
       <c r="A251" t="s">
         <v>84</v>
       </c>
-      <c r="B251">
+      <c r="B251" s="5">
         <v>45689</v>
       </c>
       <c r="C251" t="s">
@@ -11822,7 +11829,7 @@
       <c r="A252" t="s">
         <v>84</v>
       </c>
-      <c r="B252">
+      <c r="B252" s="5">
         <v>45717</v>
       </c>
       <c r="C252" t="s">
@@ -11866,7 +11873,7 @@
       <c r="A253" t="s">
         <v>84</v>
       </c>
-      <c r="B253">
+      <c r="B253" s="5">
         <v>45748</v>
       </c>
       <c r="C253" t="s">
@@ -11910,7 +11917,7 @@
       <c r="A254" t="s">
         <v>85</v>
       </c>
-      <c r="B254">
+      <c r="B254" s="5">
         <v>45658</v>
       </c>
       <c r="C254" t="s">
@@ -11954,7 +11961,7 @@
       <c r="A255" t="s">
         <v>85</v>
       </c>
-      <c r="B255">
+      <c r="B255" s="5">
         <v>45689</v>
       </c>
       <c r="C255" t="s">
@@ -11998,7 +12005,7 @@
       <c r="A256" t="s">
         <v>85</v>
       </c>
-      <c r="B256">
+      <c r="B256" s="5">
         <v>45717</v>
       </c>
       <c r="C256" t="s">
@@ -12042,7 +12049,7 @@
       <c r="A257" t="s">
         <v>85</v>
       </c>
-      <c r="B257">
+      <c r="B257" s="5">
         <v>45748</v>
       </c>
       <c r="C257" t="s">
@@ -12086,7 +12093,7 @@
       <c r="A258" t="s">
         <v>86</v>
       </c>
-      <c r="B258">
+      <c r="B258" s="5">
         <v>45658</v>
       </c>
       <c r="C258" t="s">
@@ -12130,7 +12137,7 @@
       <c r="A259" t="s">
         <v>86</v>
       </c>
-      <c r="B259">
+      <c r="B259" s="5">
         <v>45689</v>
       </c>
       <c r="C259" t="s">
@@ -12174,7 +12181,7 @@
       <c r="A260" t="s">
         <v>86</v>
       </c>
-      <c r="B260">
+      <c r="B260" s="5">
         <v>45717</v>
       </c>
       <c r="C260" t="s">
@@ -12218,7 +12225,7 @@
       <c r="A261" t="s">
         <v>86</v>
       </c>
-      <c r="B261">
+      <c r="B261" s="5">
         <v>45748</v>
       </c>
       <c r="C261" t="s">
@@ -12262,7 +12269,7 @@
       <c r="A262" t="s">
         <v>87</v>
       </c>
-      <c r="B262">
+      <c r="B262" s="5">
         <v>45658</v>
       </c>
       <c r="C262" t="s">
@@ -12306,7 +12313,7 @@
       <c r="A263" t="s">
         <v>87</v>
       </c>
-      <c r="B263">
+      <c r="B263" s="5">
         <v>45689</v>
       </c>
       <c r="C263" t="s">
@@ -12347,7 +12354,7 @@
       <c r="A264" t="s">
         <v>87</v>
       </c>
-      <c r="B264">
+      <c r="B264" s="5">
         <v>45717</v>
       </c>
       <c r="C264" t="s">
@@ -12391,7 +12398,7 @@
       <c r="A265" t="s">
         <v>87</v>
       </c>
-      <c r="B265">
+      <c r="B265" s="5">
         <v>45748</v>
       </c>
       <c r="C265" t="s">
@@ -12435,7 +12442,7 @@
       <c r="A266" t="s">
         <v>88</v>
       </c>
-      <c r="B266">
+      <c r="B266" s="5">
         <v>45658</v>
       </c>
       <c r="C266" t="s">
@@ -12479,7 +12486,7 @@
       <c r="A267" t="s">
         <v>88</v>
       </c>
-      <c r="B267">
+      <c r="B267" s="5">
         <v>45689</v>
       </c>
       <c r="C267" t="s">
@@ -12523,7 +12530,7 @@
       <c r="A268" t="s">
         <v>88</v>
       </c>
-      <c r="B268">
+      <c r="B268" s="5">
         <v>45717</v>
       </c>
       <c r="C268" t="s">
@@ -12567,7 +12574,7 @@
       <c r="A269" t="s">
         <v>88</v>
       </c>
-      <c r="B269">
+      <c r="B269" s="5">
         <v>45748</v>
       </c>
       <c r="C269" t="s">
@@ -12611,7 +12618,7 @@
       <c r="A270" t="s">
         <v>89</v>
       </c>
-      <c r="B270">
+      <c r="B270" s="5">
         <v>45658</v>
       </c>
       <c r="C270" t="s">
@@ -12655,7 +12662,7 @@
       <c r="A271" t="s">
         <v>89</v>
       </c>
-      <c r="B271">
+      <c r="B271" s="5">
         <v>45689</v>
       </c>
       <c r="C271" t="s">
@@ -12699,7 +12706,7 @@
       <c r="A272" t="s">
         <v>89</v>
       </c>
-      <c r="B272">
+      <c r="B272" s="5">
         <v>45717</v>
       </c>
       <c r="C272" t="s">
@@ -12743,7 +12750,7 @@
       <c r="A273" t="s">
         <v>89</v>
       </c>
-      <c r="B273">
+      <c r="B273" s="5">
         <v>45748</v>
       </c>
       <c r="C273" t="s">
@@ -12787,7 +12794,7 @@
       <c r="A274" t="s">
         <v>90</v>
       </c>
-      <c r="B274">
+      <c r="B274" s="5">
         <v>45658</v>
       </c>
       <c r="C274" t="s">
@@ -12831,7 +12838,7 @@
       <c r="A275" t="s">
         <v>90</v>
       </c>
-      <c r="B275">
+      <c r="B275" s="5">
         <v>45689</v>
       </c>
       <c r="C275" t="s">
@@ -12875,7 +12882,7 @@
       <c r="A276" t="s">
         <v>90</v>
       </c>
-      <c r="B276">
+      <c r="B276" s="5">
         <v>45717</v>
       </c>
       <c r="C276" t="s">
@@ -12919,7 +12926,7 @@
       <c r="A277" t="s">
         <v>90</v>
       </c>
-      <c r="B277">
+      <c r="B277" s="5">
         <v>45748</v>
       </c>
       <c r="C277" t="s">
@@ -12963,7 +12970,7 @@
       <c r="A278" t="s">
         <v>91</v>
       </c>
-      <c r="B278">
+      <c r="B278" s="5">
         <v>45658</v>
       </c>
       <c r="C278" t="s">
@@ -13007,7 +13014,7 @@
       <c r="A279" t="s">
         <v>91</v>
       </c>
-      <c r="B279">
+      <c r="B279" s="5">
         <v>45689</v>
       </c>
       <c r="C279" t="s">
@@ -13051,7 +13058,7 @@
       <c r="A280" t="s">
         <v>91</v>
       </c>
-      <c r="B280">
+      <c r="B280" s="5">
         <v>45717</v>
       </c>
       <c r="C280" t="s">
@@ -13095,7 +13102,7 @@
       <c r="A281" t="s">
         <v>91</v>
       </c>
-      <c r="B281">
+      <c r="B281" s="5">
         <v>45748</v>
       </c>
       <c r="C281" t="s">
@@ -13139,7 +13146,7 @@
       <c r="A282" t="s">
         <v>92</v>
       </c>
-      <c r="B282">
+      <c r="B282" s="5">
         <v>45658</v>
       </c>
       <c r="C282" t="s">
@@ -13183,7 +13190,7 @@
       <c r="A283" t="s">
         <v>92</v>
       </c>
-      <c r="B283">
+      <c r="B283" s="5">
         <v>45689</v>
       </c>
       <c r="C283" t="s">
@@ -13227,7 +13234,7 @@
       <c r="A284" t="s">
         <v>92</v>
       </c>
-      <c r="B284">
+      <c r="B284" s="5">
         <v>45717</v>
       </c>
       <c r="C284" t="s">
@@ -13271,7 +13278,7 @@
       <c r="A285" t="s">
         <v>92</v>
       </c>
-      <c r="B285">
+      <c r="B285" s="5">
         <v>45748</v>
       </c>
       <c r="C285" t="s">
@@ -13315,7 +13322,7 @@
       <c r="A286" t="s">
         <v>93</v>
       </c>
-      <c r="B286">
+      <c r="B286" s="5">
         <v>45658</v>
       </c>
       <c r="C286" t="s">
@@ -13359,7 +13366,7 @@
       <c r="A287" t="s">
         <v>93</v>
       </c>
-      <c r="B287">
+      <c r="B287" s="5">
         <v>45689</v>
       </c>
       <c r="C287" t="s">
@@ -13403,7 +13410,7 @@
       <c r="A288" t="s">
         <v>93</v>
       </c>
-      <c r="B288">
+      <c r="B288" s="5">
         <v>45717</v>
       </c>
       <c r="C288" t="s">
@@ -13447,7 +13454,7 @@
       <c r="A289" t="s">
         <v>93</v>
       </c>
-      <c r="B289">
+      <c r="B289" s="5">
         <v>45748</v>
       </c>
       <c r="C289" t="s">
@@ -13491,7 +13498,7 @@
       <c r="A290" t="s">
         <v>94</v>
       </c>
-      <c r="B290">
+      <c r="B290" s="5">
         <v>45658</v>
       </c>
       <c r="C290" t="s">
@@ -13535,7 +13542,7 @@
       <c r="A291" t="s">
         <v>94</v>
       </c>
-      <c r="B291">
+      <c r="B291" s="5">
         <v>45689</v>
       </c>
       <c r="C291" t="s">
@@ -13579,7 +13586,7 @@
       <c r="A292" t="s">
         <v>94</v>
       </c>
-      <c r="B292">
+      <c r="B292" s="5">
         <v>45717</v>
       </c>
       <c r="C292" t="s">
@@ -13623,7 +13630,7 @@
       <c r="A293" t="s">
         <v>94</v>
       </c>
-      <c r="B293">
+      <c r="B293" s="5">
         <v>45748</v>
       </c>
       <c r="C293" t="s">
@@ -13667,7 +13674,7 @@
       <c r="A294" t="s">
         <v>95</v>
       </c>
-      <c r="B294">
+      <c r="B294" s="5">
         <v>45658</v>
       </c>
       <c r="C294" t="s">
@@ -13711,7 +13718,7 @@
       <c r="A295" t="s">
         <v>95</v>
       </c>
-      <c r="B295">
+      <c r="B295" s="5">
         <v>45689</v>
       </c>
       <c r="C295" t="s">
@@ -13755,7 +13762,7 @@
       <c r="A296" t="s">
         <v>95</v>
       </c>
-      <c r="B296">
+      <c r="B296" s="5">
         <v>45717</v>
       </c>
       <c r="C296" t="s">
@@ -13799,7 +13806,7 @@
       <c r="A297" t="s">
         <v>95</v>
       </c>
-      <c r="B297">
+      <c r="B297" s="5">
         <v>45748</v>
       </c>
       <c r="C297" t="s">
@@ -13843,7 +13850,7 @@
       <c r="A298" t="s">
         <v>96</v>
       </c>
-      <c r="B298">
+      <c r="B298" s="5">
         <v>45658</v>
       </c>
       <c r="C298" t="s">
@@ -13887,7 +13894,7 @@
       <c r="A299" t="s">
         <v>96</v>
       </c>
-      <c r="B299">
+      <c r="B299" s="5">
         <v>45689</v>
       </c>
       <c r="C299" t="s">
@@ -13931,7 +13938,7 @@
       <c r="A300" t="s">
         <v>96</v>
       </c>
-      <c r="B300">
+      <c r="B300" s="5">
         <v>45717</v>
       </c>
       <c r="C300" t="s">
@@ -13975,7 +13982,7 @@
       <c r="A301" t="s">
         <v>96</v>
       </c>
-      <c r="B301">
+      <c r="B301" s="5">
         <v>45748</v>
       </c>
       <c r="C301" t="s">
@@ -14019,7 +14026,7 @@
       <c r="A302" t="s">
         <v>97</v>
       </c>
-      <c r="B302">
+      <c r="B302" s="5">
         <v>45658</v>
       </c>
       <c r="C302" t="s">
@@ -14063,7 +14070,7 @@
       <c r="A303" t="s">
         <v>97</v>
       </c>
-      <c r="B303">
+      <c r="B303" s="5">
         <v>45689</v>
       </c>
       <c r="C303" t="s">
@@ -14107,7 +14114,7 @@
       <c r="A304" t="s">
         <v>97</v>
       </c>
-      <c r="B304">
+      <c r="B304" s="5">
         <v>45717</v>
       </c>
       <c r="C304" t="s">
@@ -14151,7 +14158,7 @@
       <c r="A305" t="s">
         <v>97</v>
       </c>
-      <c r="B305">
+      <c r="B305" s="5">
         <v>45748</v>
       </c>
       <c r="C305" t="s">
@@ -14195,7 +14202,7 @@
       <c r="A306" t="s">
         <v>98</v>
       </c>
-      <c r="B306">
+      <c r="B306" s="5">
         <v>45658</v>
       </c>
       <c r="C306" t="s">
@@ -14239,7 +14246,7 @@
       <c r="A307" t="s">
         <v>98</v>
       </c>
-      <c r="B307">
+      <c r="B307" s="5">
         <v>45689</v>
       </c>
       <c r="C307" t="s">
@@ -14283,7 +14290,7 @@
       <c r="A308" t="s">
         <v>98</v>
       </c>
-      <c r="B308">
+      <c r="B308" s="5">
         <v>45717</v>
       </c>
       <c r="C308" t="s">
@@ -14327,7 +14334,7 @@
       <c r="A309" t="s">
         <v>98</v>
       </c>
-      <c r="B309">
+      <c r="B309" s="5">
         <v>45748</v>
       </c>
       <c r="C309" t="s">
@@ -14371,7 +14378,7 @@
       <c r="A310" t="s">
         <v>99</v>
       </c>
-      <c r="B310">
+      <c r="B310" s="5">
         <v>45658</v>
       </c>
       <c r="C310" t="s">
@@ -14415,7 +14422,7 @@
       <c r="A311" t="s">
         <v>99</v>
       </c>
-      <c r="B311">
+      <c r="B311" s="5">
         <v>45689</v>
       </c>
       <c r="C311" t="s">
@@ -14459,7 +14466,7 @@
       <c r="A312" t="s">
         <v>99</v>
       </c>
-      <c r="B312">
+      <c r="B312" s="5">
         <v>45717</v>
       </c>
       <c r="C312" t="s">
@@ -14503,7 +14510,7 @@
       <c r="A313" t="s">
         <v>99</v>
       </c>
-      <c r="B313">
+      <c r="B313" s="5">
         <v>45748</v>
       </c>
       <c r="C313" t="s">
@@ -14544,7 +14551,7 @@
       <c r="A314" t="s">
         <v>100</v>
       </c>
-      <c r="B314">
+      <c r="B314" s="5">
         <v>45658</v>
       </c>
       <c r="C314" t="s">
@@ -14588,7 +14595,7 @@
       <c r="A315" t="s">
         <v>100</v>
       </c>
-      <c r="B315">
+      <c r="B315" s="5">
         <v>45689</v>
       </c>
       <c r="C315" t="s">
@@ -14629,7 +14636,7 @@
       <c r="A316" t="s">
         <v>100</v>
       </c>
-      <c r="B316">
+      <c r="B316" s="5">
         <v>45717</v>
       </c>
       <c r="C316" t="s">
@@ -14673,7 +14680,7 @@
       <c r="A317" t="s">
         <v>100</v>
       </c>
-      <c r="B317">
+      <c r="B317" s="5">
         <v>45748</v>
       </c>
       <c r="C317" t="s">
@@ -14717,7 +14724,7 @@
       <c r="A318" t="s">
         <v>101</v>
       </c>
-      <c r="B318">
+      <c r="B318" s="5">
         <v>45658</v>
       </c>
       <c r="C318" t="s">
@@ -14761,7 +14768,7 @@
       <c r="A319" t="s">
         <v>101</v>
       </c>
-      <c r="B319">
+      <c r="B319" s="5">
         <v>45689</v>
       </c>
       <c r="C319" t="s">
@@ -14805,7 +14812,7 @@
       <c r="A320" t="s">
         <v>101</v>
       </c>
-      <c r="B320">
+      <c r="B320" s="5">
         <v>45717</v>
       </c>
       <c r="C320" t="s">
@@ -14849,7 +14856,7 @@
       <c r="A321" t="s">
         <v>101</v>
       </c>
-      <c r="B321">
+      <c r="B321" s="5">
         <v>45748</v>
       </c>
       <c r="C321" t="s">
@@ -14899,6 +14906,7 @@
   <dimension ref="A1:AN323"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -14932,7 +14940,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -15036,7 +15044,7 @@
       <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="5">
         <v>45658</v>
       </c>
       <c r="C2" t="s">
@@ -15152,7 +15160,7 @@
       <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="5">
         <v>45689</v>
       </c>
       <c r="C3" t="s">
@@ -15268,7 +15276,7 @@
       <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="5">
         <v>45717</v>
       </c>
       <c r="C4" t="s">
@@ -15384,7 +15392,7 @@
       <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="5">
         <v>45748</v>
       </c>
       <c r="C5" t="s">
@@ -15500,7 +15508,7 @@
       <c r="A6" t="s">
         <v>17</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="5">
         <v>45658</v>
       </c>
       <c r="C6" t="s">
@@ -15616,7 +15624,7 @@
       <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="5">
         <v>45689</v>
       </c>
       <c r="C7" t="s">
@@ -15732,7 +15740,7 @@
       <c r="A8" t="s">
         <v>17</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="5">
         <v>45717</v>
       </c>
       <c r="C8" t="s">
@@ -15848,7 +15856,7 @@
       <c r="A9" t="s">
         <v>17</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="5">
         <v>45748</v>
       </c>
       <c r="C9" t="s">
@@ -15964,7 +15972,7 @@
       <c r="A10" t="s">
         <v>19</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="5">
         <v>45658</v>
       </c>
       <c r="C10" t="s">
@@ -16080,7 +16088,7 @@
       <c r="A11" t="s">
         <v>19</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="5">
         <v>45689</v>
       </c>
       <c r="C11" t="s">
@@ -16196,7 +16204,7 @@
       <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="5">
         <v>45717</v>
       </c>
       <c r="C12" t="s">
@@ -16312,7 +16320,7 @@
       <c r="A13" t="s">
         <v>19</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="5">
         <v>45748</v>
       </c>
       <c r="C13" t="s">
@@ -16428,7 +16436,7 @@
       <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="5">
         <v>45658</v>
       </c>
       <c r="C14" t="s">
@@ -16544,7 +16552,7 @@
       <c r="A15" t="s">
         <v>22</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="5">
         <v>45689</v>
       </c>
       <c r="C15" t="s">
@@ -16660,7 +16668,7 @@
       <c r="A16" t="s">
         <v>22</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="5">
         <v>45717</v>
       </c>
       <c r="C16" t="s">
@@ -16776,7 +16784,7 @@
       <c r="A17" t="s">
         <v>22</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="5">
         <v>45748</v>
       </c>
       <c r="C17" t="s">
@@ -16892,7 +16900,7 @@
       <c r="A18" t="s">
         <v>23</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="5">
         <v>45658</v>
       </c>
       <c r="C18" t="s">
@@ -17008,7 +17016,7 @@
       <c r="A19" t="s">
         <v>23</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="5">
         <v>45689</v>
       </c>
       <c r="C19" t="s">
@@ -17124,7 +17132,7 @@
       <c r="A20" t="s">
         <v>23</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="5">
         <v>45717</v>
       </c>
       <c r="C20" t="s">
@@ -17240,7 +17248,7 @@
       <c r="A21" t="s">
         <v>23</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="5">
         <v>45748</v>
       </c>
       <c r="C21" t="s">
@@ -17356,7 +17364,7 @@
       <c r="A22" t="s">
         <v>25</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="5">
         <v>45658</v>
       </c>
       <c r="C22" t="s">
@@ -17472,7 +17480,7 @@
       <c r="A23" t="s">
         <v>25</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="5">
         <v>45689</v>
       </c>
       <c r="C23" t="s">
@@ -17588,7 +17596,7 @@
       <c r="A24" t="s">
         <v>25</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="5">
         <v>45717</v>
       </c>
       <c r="C24" t="s">
@@ -17704,7 +17712,7 @@
       <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="5">
         <v>45748</v>
       </c>
       <c r="C25" t="s">
@@ -17820,7 +17828,7 @@
       <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="5">
         <v>45658</v>
       </c>
       <c r="C26" t="s">
@@ -17936,7 +17944,7 @@
       <c r="A27" t="s">
         <v>26</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="5">
         <v>45689</v>
       </c>
       <c r="C27" t="s">
@@ -18052,7 +18060,7 @@
       <c r="A28" t="s">
         <v>26</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="5">
         <v>45717</v>
       </c>
       <c r="C28" t="s">
@@ -18168,7 +18176,7 @@
       <c r="A29" t="s">
         <v>26</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="5">
         <v>45748</v>
       </c>
       <c r="C29" t="s">
@@ -18284,7 +18292,7 @@
       <c r="A30" t="s">
         <v>29</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="5">
         <v>45658</v>
       </c>
       <c r="C30" t="s">
@@ -18400,7 +18408,7 @@
       <c r="A31" t="s">
         <v>29</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="5">
         <v>45689</v>
       </c>
       <c r="C31" t="s">
@@ -18516,7 +18524,7 @@
       <c r="A32" t="s">
         <v>29</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="5">
         <v>45717</v>
       </c>
       <c r="C32" t="s">
@@ -18632,7 +18640,7 @@
       <c r="A33" t="s">
         <v>29</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="5">
         <v>45748</v>
       </c>
       <c r="C33" t="s">
@@ -18748,7 +18756,7 @@
       <c r="A34" t="s">
         <v>30</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="5">
         <v>45658</v>
       </c>
       <c r="C34" t="s">
@@ -18864,7 +18872,7 @@
       <c r="A35" t="s">
         <v>30</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="5">
         <v>45689</v>
       </c>
       <c r="C35" t="s">
@@ -18980,7 +18988,7 @@
       <c r="A36" t="s">
         <v>30</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="5">
         <v>45717</v>
       </c>
       <c r="C36" t="s">
@@ -19096,7 +19104,7 @@
       <c r="A37" t="s">
         <v>30</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="5">
         <v>45748</v>
       </c>
       <c r="C37" t="s">
@@ -19212,7 +19220,7 @@
       <c r="A38" t="s">
         <v>31</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="5">
         <v>45658</v>
       </c>
       <c r="C38" t="s">
@@ -19328,7 +19336,7 @@
       <c r="A39" t="s">
         <v>31</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="5">
         <v>45689</v>
       </c>
       <c r="C39" t="s">
@@ -19444,7 +19452,7 @@
       <c r="A40" t="s">
         <v>31</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="5">
         <v>45717</v>
       </c>
       <c r="C40" t="s">
@@ -19560,7 +19568,7 @@
       <c r="A41" t="s">
         <v>31</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="5">
         <v>45748</v>
       </c>
       <c r="C41" t="s">
@@ -19676,7 +19684,7 @@
       <c r="A42" t="s">
         <v>32</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="5">
         <v>45658</v>
       </c>
       <c r="C42" t="s">
@@ -19792,7 +19800,7 @@
       <c r="A43" t="s">
         <v>32</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="5">
         <v>45689</v>
       </c>
       <c r="C43" t="s">
@@ -19908,7 +19916,7 @@
       <c r="A44" t="s">
         <v>32</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="5">
         <v>45717</v>
       </c>
       <c r="C44" t="s">
@@ -20024,7 +20032,7 @@
       <c r="A45" t="s">
         <v>32</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="5">
         <v>45748</v>
       </c>
       <c r="C45" t="s">
@@ -20140,7 +20148,7 @@
       <c r="A46" t="s">
         <v>33</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="5">
         <v>45658</v>
       </c>
       <c r="C46" t="s">
@@ -20256,7 +20264,7 @@
       <c r="A47" t="s">
         <v>33</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="5">
         <v>45689</v>
       </c>
       <c r="C47" t="s">
@@ -20372,7 +20380,7 @@
       <c r="A48" t="s">
         <v>33</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="5">
         <v>45717</v>
       </c>
       <c r="C48" t="s">
@@ -20488,7 +20496,7 @@
       <c r="A49" t="s">
         <v>33</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="5">
         <v>45748</v>
       </c>
       <c r="C49" t="s">
@@ -20604,7 +20612,7 @@
       <c r="A50" t="s">
         <v>34</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="5">
         <v>45658</v>
       </c>
       <c r="C50" t="s">
@@ -20720,7 +20728,7 @@
       <c r="A51" t="s">
         <v>34</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="5">
         <v>45689</v>
       </c>
       <c r="C51" t="s">
@@ -20836,7 +20844,7 @@
       <c r="A52" t="s">
         <v>34</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="5">
         <v>45717</v>
       </c>
       <c r="C52" t="s">
@@ -20952,7 +20960,7 @@
       <c r="A53" t="s">
         <v>34</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="5">
         <v>45748</v>
       </c>
       <c r="C53" t="s">
@@ -21068,7 +21076,7 @@
       <c r="A54" t="s">
         <v>35</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="5">
         <v>45658</v>
       </c>
       <c r="C54" t="s">
@@ -21184,7 +21192,7 @@
       <c r="A55" t="s">
         <v>35</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="5">
         <v>45689</v>
       </c>
       <c r="C55" t="s">
@@ -21300,7 +21308,7 @@
       <c r="A56" t="s">
         <v>35</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="5">
         <v>45717</v>
       </c>
       <c r="C56" t="s">
@@ -21416,7 +21424,7 @@
       <c r="A57" t="s">
         <v>35</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="5">
         <v>45748</v>
       </c>
       <c r="C57" t="s">
@@ -21532,7 +21540,7 @@
       <c r="A58" t="s">
         <v>36</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="5">
         <v>45658</v>
       </c>
       <c r="C58" t="s">
@@ -21648,7 +21656,7 @@
       <c r="A59" t="s">
         <v>36</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="5">
         <v>45689</v>
       </c>
       <c r="C59" t="s">
@@ -21764,7 +21772,7 @@
       <c r="A60" t="s">
         <v>36</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="5">
         <v>45717</v>
       </c>
       <c r="C60" t="s">
@@ -21880,7 +21888,7 @@
       <c r="A61" t="s">
         <v>36</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="5">
         <v>45748</v>
       </c>
       <c r="C61" t="s">
@@ -21996,7 +22004,7 @@
       <c r="A62" t="s">
         <v>37</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="5">
         <v>45658</v>
       </c>
       <c r="C62" t="s">
@@ -22112,7 +22120,7 @@
       <c r="A63" t="s">
         <v>37</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="5">
         <v>45689</v>
       </c>
       <c r="C63" t="s">
@@ -22228,7 +22236,7 @@
       <c r="A64" t="s">
         <v>37</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="5">
         <v>45717</v>
       </c>
       <c r="C64" t="s">
@@ -22344,7 +22352,7 @@
       <c r="A65" t="s">
         <v>37</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="5">
         <v>45748</v>
       </c>
       <c r="C65" t="s">
@@ -22460,7 +22468,7 @@
       <c r="A66" t="s">
         <v>38</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="5">
         <v>45658</v>
       </c>
       <c r="C66" t="s">
@@ -22576,7 +22584,7 @@
       <c r="A67" t="s">
         <v>38</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="5">
         <v>45689</v>
       </c>
       <c r="C67" t="s">
@@ -22692,7 +22700,7 @@
       <c r="A68" t="s">
         <v>38</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="5">
         <v>45717</v>
       </c>
       <c r="C68" t="s">
@@ -22808,7 +22816,7 @@
       <c r="A69" t="s">
         <v>38</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="5">
         <v>45748</v>
       </c>
       <c r="C69" t="s">
@@ -22924,7 +22932,7 @@
       <c r="A70" t="s">
         <v>39</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="5">
         <v>45658</v>
       </c>
       <c r="C70" t="s">
@@ -23040,7 +23048,7 @@
       <c r="A71" t="s">
         <v>39</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="5">
         <v>45689</v>
       </c>
       <c r="C71" t="s">
@@ -23156,7 +23164,7 @@
       <c r="A72" t="s">
         <v>39</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="5">
         <v>45717</v>
       </c>
       <c r="C72" t="s">
@@ -23272,7 +23280,7 @@
       <c r="A73" t="s">
         <v>39</v>
       </c>
-      <c r="B73">
+      <c r="B73" s="5">
         <v>45748</v>
       </c>
       <c r="C73" t="s">
@@ -23388,7 +23396,7 @@
       <c r="A74" t="s">
         <v>40</v>
       </c>
-      <c r="B74">
+      <c r="B74" s="5">
         <v>45658</v>
       </c>
       <c r="C74" t="s">
@@ -23504,7 +23512,7 @@
       <c r="A75" t="s">
         <v>40</v>
       </c>
-      <c r="B75">
+      <c r="B75" s="5">
         <v>45689</v>
       </c>
       <c r="C75" t="s">
@@ -23620,7 +23628,7 @@
       <c r="A76" t="s">
         <v>40</v>
       </c>
-      <c r="B76">
+      <c r="B76" s="5">
         <v>45717</v>
       </c>
       <c r="C76" t="s">
@@ -23736,7 +23744,7 @@
       <c r="A77" t="s">
         <v>40</v>
       </c>
-      <c r="B77">
+      <c r="B77" s="5">
         <v>45748</v>
       </c>
       <c r="C77" t="s">
@@ -23852,7 +23860,7 @@
       <c r="A78" t="s">
         <v>41</v>
       </c>
-      <c r="B78">
+      <c r="B78" s="5">
         <v>45658</v>
       </c>
       <c r="C78" t="s">
@@ -23968,7 +23976,7 @@
       <c r="A79" t="s">
         <v>41</v>
       </c>
-      <c r="B79">
+      <c r="B79" s="5">
         <v>45689</v>
       </c>
       <c r="C79" t="s">
@@ -24084,7 +24092,7 @@
       <c r="A80" t="s">
         <v>41</v>
       </c>
-      <c r="B80">
+      <c r="B80" s="5">
         <v>45717</v>
       </c>
       <c r="C80" t="s">
@@ -24200,7 +24208,7 @@
       <c r="A81" t="s">
         <v>41</v>
       </c>
-      <c r="B81">
+      <c r="B81" s="5">
         <v>45748</v>
       </c>
       <c r="C81" t="s">
@@ -24316,7 +24324,7 @@
       <c r="A82" t="s">
         <v>42</v>
       </c>
-      <c r="B82">
+      <c r="B82" s="5">
         <v>45658</v>
       </c>
       <c r="C82" t="s">
@@ -24432,7 +24440,7 @@
       <c r="A83" t="s">
         <v>42</v>
       </c>
-      <c r="B83">
+      <c r="B83" s="5">
         <v>45689</v>
       </c>
       <c r="C83" t="s">
@@ -24548,7 +24556,7 @@
       <c r="A84" t="s">
         <v>42</v>
       </c>
-      <c r="B84">
+      <c r="B84" s="5">
         <v>45717</v>
       </c>
       <c r="C84" t="s">
@@ -24664,7 +24672,7 @@
       <c r="A85" t="s">
         <v>42</v>
       </c>
-      <c r="B85">
+      <c r="B85" s="5">
         <v>45748</v>
       </c>
       <c r="C85" t="s">
@@ -24780,7 +24788,7 @@
       <c r="A86" t="s">
         <v>43</v>
       </c>
-      <c r="B86">
+      <c r="B86" s="5">
         <v>45658</v>
       </c>
       <c r="C86" t="s">
@@ -24896,7 +24904,7 @@
       <c r="A87" t="s">
         <v>43</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="5">
         <v>45689</v>
       </c>
       <c r="C87" t="s">
@@ -25012,7 +25020,7 @@
       <c r="A88" t="s">
         <v>43</v>
       </c>
-      <c r="B88">
+      <c r="B88" s="5">
         <v>45717</v>
       </c>
       <c r="C88" t="s">
@@ -25128,7 +25136,7 @@
       <c r="A89" t="s">
         <v>43</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="5">
         <v>45748</v>
       </c>
       <c r="C89" t="s">
@@ -25244,7 +25252,7 @@
       <c r="A90" t="s">
         <v>44</v>
       </c>
-      <c r="B90">
+      <c r="B90" s="5">
         <v>45658</v>
       </c>
       <c r="C90" t="s">
@@ -25360,7 +25368,7 @@
       <c r="A91" t="s">
         <v>44</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="5">
         <v>45689</v>
       </c>
       <c r="C91" t="s">
@@ -25476,7 +25484,7 @@
       <c r="A92" t="s">
         <v>44</v>
       </c>
-      <c r="B92">
+      <c r="B92" s="5">
         <v>45717</v>
       </c>
       <c r="C92" t="s">
@@ -25592,7 +25600,7 @@
       <c r="A93" t="s">
         <v>44</v>
       </c>
-      <c r="B93">
+      <c r="B93" s="5">
         <v>45748</v>
       </c>
       <c r="C93" t="s">
@@ -25708,7 +25716,7 @@
       <c r="A94" t="s">
         <v>45</v>
       </c>
-      <c r="B94">
+      <c r="B94" s="5">
         <v>45658</v>
       </c>
       <c r="C94" t="s">
@@ -25824,7 +25832,7 @@
       <c r="A95" t="s">
         <v>45</v>
       </c>
-      <c r="B95">
+      <c r="B95" s="5">
         <v>45689</v>
       </c>
       <c r="C95" t="s">
@@ -25940,7 +25948,7 @@
       <c r="A96" t="s">
         <v>45</v>
       </c>
-      <c r="B96">
+      <c r="B96" s="5">
         <v>45717</v>
       </c>
       <c r="C96" t="s">
@@ -26056,7 +26064,7 @@
       <c r="A97" t="s">
         <v>45</v>
       </c>
-      <c r="B97">
+      <c r="B97" s="5">
         <v>45748</v>
       </c>
       <c r="C97" t="s">
@@ -26172,7 +26180,7 @@
       <c r="A98" t="s">
         <v>46</v>
       </c>
-      <c r="B98">
+      <c r="B98" s="5">
         <v>45658</v>
       </c>
       <c r="C98" t="s">
@@ -26288,7 +26296,7 @@
       <c r="A99" t="s">
         <v>46</v>
       </c>
-      <c r="B99">
+      <c r="B99" s="5">
         <v>45689</v>
       </c>
       <c r="C99" t="s">
@@ -26404,7 +26412,7 @@
       <c r="A100" t="s">
         <v>46</v>
       </c>
-      <c r="B100">
+      <c r="B100" s="5">
         <v>45717</v>
       </c>
       <c r="C100" t="s">
@@ -26520,7 +26528,7 @@
       <c r="A101" t="s">
         <v>46</v>
       </c>
-      <c r="B101">
+      <c r="B101" s="5">
         <v>45748</v>
       </c>
       <c r="C101" t="s">
@@ -26636,7 +26644,7 @@
       <c r="A102" t="s">
         <v>47</v>
       </c>
-      <c r="B102">
+      <c r="B102" s="5">
         <v>45658</v>
       </c>
       <c r="C102" t="s">
@@ -26752,7 +26760,7 @@
       <c r="A103" t="s">
         <v>47</v>
       </c>
-      <c r="B103">
+      <c r="B103" s="5">
         <v>45689</v>
       </c>
       <c r="C103" t="s">
@@ -26868,7 +26876,7 @@
       <c r="A104" t="s">
         <v>47</v>
       </c>
-      <c r="B104">
+      <c r="B104" s="5">
         <v>45717</v>
       </c>
       <c r="C104" t="s">
@@ -26984,7 +26992,7 @@
       <c r="A105" t="s">
         <v>47</v>
       </c>
-      <c r="B105">
+      <c r="B105" s="5">
         <v>45748</v>
       </c>
       <c r="C105" t="s">
@@ -27100,7 +27108,7 @@
       <c r="A106" t="s">
         <v>48</v>
       </c>
-      <c r="B106">
+      <c r="B106" s="5">
         <v>45658</v>
       </c>
       <c r="C106" t="s">
@@ -27216,7 +27224,7 @@
       <c r="A107" t="s">
         <v>48</v>
       </c>
-      <c r="B107">
+      <c r="B107" s="5">
         <v>45689</v>
       </c>
       <c r="C107" t="s">
@@ -27332,7 +27340,7 @@
       <c r="A108" t="s">
         <v>48</v>
       </c>
-      <c r="B108">
+      <c r="B108" s="5">
         <v>45717</v>
       </c>
       <c r="C108" t="s">
@@ -27448,7 +27456,7 @@
       <c r="A109" t="s">
         <v>48</v>
       </c>
-      <c r="B109">
+      <c r="B109" s="5">
         <v>45748</v>
       </c>
       <c r="C109" t="s">
@@ -27564,7 +27572,7 @@
       <c r="A110" t="s">
         <v>49</v>
       </c>
-      <c r="B110">
+      <c r="B110" s="5">
         <v>45658</v>
       </c>
       <c r="C110" t="s">
@@ -27680,7 +27688,7 @@
       <c r="A111" t="s">
         <v>49</v>
       </c>
-      <c r="B111">
+      <c r="B111" s="5">
         <v>45689</v>
       </c>
       <c r="C111" t="s">
@@ -27796,7 +27804,7 @@
       <c r="A112" t="s">
         <v>49</v>
       </c>
-      <c r="B112">
+      <c r="B112" s="5">
         <v>45717</v>
       </c>
       <c r="C112" t="s">
@@ -27912,7 +27920,7 @@
       <c r="A113" t="s">
         <v>49</v>
       </c>
-      <c r="B113">
+      <c r="B113" s="5">
         <v>45748</v>
       </c>
       <c r="C113" t="s">
@@ -28028,7 +28036,7 @@
       <c r="A114" t="s">
         <v>50</v>
       </c>
-      <c r="B114">
+      <c r="B114" s="5">
         <v>45658</v>
       </c>
       <c r="C114" t="s">
@@ -28144,7 +28152,7 @@
       <c r="A115" t="s">
         <v>50</v>
       </c>
-      <c r="B115">
+      <c r="B115" s="5">
         <v>45689</v>
       </c>
       <c r="C115" t="s">
@@ -28260,7 +28268,7 @@
       <c r="A116" t="s">
         <v>50</v>
       </c>
-      <c r="B116">
+      <c r="B116" s="5">
         <v>45717</v>
       </c>
       <c r="C116" t="s">
@@ -28376,7 +28384,7 @@
       <c r="A117" t="s">
         <v>50</v>
       </c>
-      <c r="B117">
+      <c r="B117" s="5">
         <v>45748</v>
       </c>
       <c r="C117" t="s">
@@ -28492,7 +28500,7 @@
       <c r="A118" t="s">
         <v>51</v>
       </c>
-      <c r="B118">
+      <c r="B118" s="5">
         <v>45658</v>
       </c>
       <c r="C118" t="s">
@@ -28608,7 +28616,7 @@
       <c r="A119" t="s">
         <v>51</v>
       </c>
-      <c r="B119">
+      <c r="B119" s="5">
         <v>45689</v>
       </c>
       <c r="C119" t="s">
@@ -28724,7 +28732,7 @@
       <c r="A120" t="s">
         <v>51</v>
       </c>
-      <c r="B120">
+      <c r="B120" s="5">
         <v>45717</v>
       </c>
       <c r="C120" t="s">
@@ -28840,7 +28848,7 @@
       <c r="A121" t="s">
         <v>51</v>
       </c>
-      <c r="B121">
+      <c r="B121" s="5">
         <v>45748</v>
       </c>
       <c r="C121" t="s">
@@ -28956,7 +28964,7 @@
       <c r="A122" t="s">
         <v>52</v>
       </c>
-      <c r="B122">
+      <c r="B122" s="5">
         <v>45658</v>
       </c>
       <c r="C122" t="s">
@@ -29072,7 +29080,7 @@
       <c r="A123" t="s">
         <v>52</v>
       </c>
-      <c r="B123">
+      <c r="B123" s="5">
         <v>45689</v>
       </c>
       <c r="C123" t="s">
@@ -29188,7 +29196,7 @@
       <c r="A124" t="s">
         <v>52</v>
       </c>
-      <c r="B124">
+      <c r="B124" s="5">
         <v>45717</v>
       </c>
       <c r="C124" t="s">
@@ -29304,7 +29312,7 @@
       <c r="A125" t="s">
         <v>52</v>
       </c>
-      <c r="B125">
+      <c r="B125" s="5">
         <v>45748</v>
       </c>
       <c r="C125" t="s">
@@ -29420,7 +29428,7 @@
       <c r="A126" t="s">
         <v>53</v>
       </c>
-      <c r="B126">
+      <c r="B126" s="5">
         <v>45658</v>
       </c>
       <c r="C126" t="s">
@@ -29536,7 +29544,7 @@
       <c r="A127" t="s">
         <v>53</v>
       </c>
-      <c r="B127">
+      <c r="B127" s="5">
         <v>45689</v>
       </c>
       <c r="C127" t="s">
@@ -29652,7 +29660,7 @@
       <c r="A128" t="s">
         <v>53</v>
       </c>
-      <c r="B128">
+      <c r="B128" s="5">
         <v>45717</v>
       </c>
       <c r="C128" t="s">
@@ -29768,7 +29776,7 @@
       <c r="A129" t="s">
         <v>53</v>
       </c>
-      <c r="B129">
+      <c r="B129" s="5">
         <v>45748</v>
       </c>
       <c r="C129" t="s">
@@ -29884,7 +29892,7 @@
       <c r="A130" t="s">
         <v>54</v>
       </c>
-      <c r="B130">
+      <c r="B130" s="5">
         <v>45658</v>
       </c>
       <c r="C130" t="s">
@@ -30000,7 +30008,7 @@
       <c r="A131" t="s">
         <v>54</v>
       </c>
-      <c r="B131">
+      <c r="B131" s="5">
         <v>45689</v>
       </c>
       <c r="C131" t="s">
@@ -30116,7 +30124,7 @@
       <c r="A132" t="s">
         <v>54</v>
       </c>
-      <c r="B132">
+      <c r="B132" s="5">
         <v>45717</v>
       </c>
       <c r="C132" t="s">
@@ -30232,7 +30240,7 @@
       <c r="A133" t="s">
         <v>54</v>
       </c>
-      <c r="B133">
+      <c r="B133" s="5">
         <v>45748</v>
       </c>
       <c r="C133" t="s">
@@ -30348,7 +30356,7 @@
       <c r="A134" t="s">
         <v>55</v>
       </c>
-      <c r="B134">
+      <c r="B134" s="5">
         <v>45658</v>
       </c>
       <c r="C134" t="s">
@@ -30464,7 +30472,7 @@
       <c r="A135" t="s">
         <v>55</v>
       </c>
-      <c r="B135">
+      <c r="B135" s="5">
         <v>45689</v>
       </c>
       <c r="C135" t="s">
@@ -30580,7 +30588,7 @@
       <c r="A136" t="s">
         <v>55</v>
       </c>
-      <c r="B136">
+      <c r="B136" s="5">
         <v>45717</v>
       </c>
       <c r="C136" t="s">
@@ -30696,7 +30704,7 @@
       <c r="A137" t="s">
         <v>55</v>
       </c>
-      <c r="B137">
+      <c r="B137" s="5">
         <v>45748</v>
       </c>
       <c r="C137" t="s">
@@ -30812,7 +30820,7 @@
       <c r="A138" t="s">
         <v>56</v>
       </c>
-      <c r="B138">
+      <c r="B138" s="5">
         <v>45658</v>
       </c>
       <c r="C138" t="s">
@@ -30928,7 +30936,7 @@
       <c r="A139" t="s">
         <v>56</v>
       </c>
-      <c r="B139">
+      <c r="B139" s="5">
         <v>45689</v>
       </c>
       <c r="C139" t="s">
@@ -31044,7 +31052,7 @@
       <c r="A140" t="s">
         <v>56</v>
       </c>
-      <c r="B140">
+      <c r="B140" s="5">
         <v>45717</v>
       </c>
       <c r="C140" t="s">
@@ -31160,7 +31168,7 @@
       <c r="A141" t="s">
         <v>56</v>
       </c>
-      <c r="B141">
+      <c r="B141" s="5">
         <v>45748</v>
       </c>
       <c r="C141" t="s">
@@ -31276,7 +31284,7 @@
       <c r="A142" t="s">
         <v>57</v>
       </c>
-      <c r="B142">
+      <c r="B142" s="5">
         <v>45658</v>
       </c>
       <c r="C142" t="s">
@@ -31392,7 +31400,7 @@
       <c r="A143" t="s">
         <v>57</v>
       </c>
-      <c r="B143">
+      <c r="B143" s="5">
         <v>45689</v>
       </c>
       <c r="C143" t="s">
@@ -31508,7 +31516,7 @@
       <c r="A144" t="s">
         <v>57</v>
       </c>
-      <c r="B144">
+      <c r="B144" s="5">
         <v>45717</v>
       </c>
       <c r="C144" t="s">
@@ -31624,7 +31632,7 @@
       <c r="A145" t="s">
         <v>57</v>
       </c>
-      <c r="B145">
+      <c r="B145" s="5">
         <v>45748</v>
       </c>
       <c r="C145" t="s">
@@ -31740,7 +31748,7 @@
       <c r="A146" t="s">
         <v>58</v>
       </c>
-      <c r="B146">
+      <c r="B146" s="5">
         <v>45658</v>
       </c>
       <c r="C146" t="s">
@@ -31856,7 +31864,7 @@
       <c r="A147" t="s">
         <v>58</v>
       </c>
-      <c r="B147">
+      <c r="B147" s="5">
         <v>45689</v>
       </c>
       <c r="C147" t="s">
@@ -31972,7 +31980,7 @@
       <c r="A148" t="s">
         <v>58</v>
       </c>
-      <c r="B148">
+      <c r="B148" s="5">
         <v>45717</v>
       </c>
       <c r="C148" t="s">
@@ -32088,7 +32096,7 @@
       <c r="A149" t="s">
         <v>58</v>
       </c>
-      <c r="B149">
+      <c r="B149" s="5">
         <v>45748</v>
       </c>
       <c r="C149" t="s">
@@ -32204,7 +32212,7 @@
       <c r="A150" t="s">
         <v>59</v>
       </c>
-      <c r="B150">
+      <c r="B150" s="5">
         <v>45658</v>
       </c>
       <c r="C150" t="s">
@@ -32320,7 +32328,7 @@
       <c r="A151" t="s">
         <v>59</v>
       </c>
-      <c r="B151">
+      <c r="B151" s="5">
         <v>45689</v>
       </c>
       <c r="C151" t="s">
@@ -32436,7 +32444,7 @@
       <c r="A152" t="s">
         <v>59</v>
       </c>
-      <c r="B152">
+      <c r="B152" s="5">
         <v>45717</v>
       </c>
       <c r="C152" t="s">
@@ -32552,7 +32560,7 @@
       <c r="A153" t="s">
         <v>59</v>
       </c>
-      <c r="B153">
+      <c r="B153" s="5">
         <v>45748</v>
       </c>
       <c r="C153" t="s">
@@ -32668,7 +32676,7 @@
       <c r="A154" t="s">
         <v>60</v>
       </c>
-      <c r="B154">
+      <c r="B154" s="5">
         <v>45658</v>
       </c>
       <c r="C154" t="s">
@@ -32784,7 +32792,7 @@
       <c r="A155" t="s">
         <v>60</v>
       </c>
-      <c r="B155">
+      <c r="B155" s="5">
         <v>45689</v>
       </c>
       <c r="C155" t="s">
@@ -32900,7 +32908,7 @@
       <c r="A156" t="s">
         <v>60</v>
       </c>
-      <c r="B156">
+      <c r="B156" s="5">
         <v>45717</v>
       </c>
       <c r="C156" t="s">
@@ -33016,7 +33024,7 @@
       <c r="A157" t="s">
         <v>60</v>
       </c>
-      <c r="B157">
+      <c r="B157" s="5">
         <v>45748</v>
       </c>
       <c r="C157" t="s">
@@ -33132,7 +33140,7 @@
       <c r="A158" t="s">
         <v>61</v>
       </c>
-      <c r="B158">
+      <c r="B158" s="5">
         <v>45658</v>
       </c>
       <c r="C158" t="s">
@@ -33248,7 +33256,7 @@
       <c r="A159" t="s">
         <v>61</v>
       </c>
-      <c r="B159">
+      <c r="B159" s="5">
         <v>45689</v>
       </c>
       <c r="C159" t="s">
@@ -33364,7 +33372,7 @@
       <c r="A160" t="s">
         <v>61</v>
       </c>
-      <c r="B160">
+      <c r="B160" s="5">
         <v>45717</v>
       </c>
       <c r="C160" t="s">
@@ -33480,7 +33488,7 @@
       <c r="A161" t="s">
         <v>61</v>
       </c>
-      <c r="B161">
+      <c r="B161" s="5">
         <v>45748</v>
       </c>
       <c r="C161" t="s">
@@ -33596,7 +33604,7 @@
       <c r="A162" t="s">
         <v>62</v>
       </c>
-      <c r="B162">
+      <c r="B162" s="5">
         <v>45658</v>
       </c>
       <c r="C162" t="s">
@@ -33712,7 +33720,7 @@
       <c r="A163" t="s">
         <v>62</v>
       </c>
-      <c r="B163">
+      <c r="B163" s="5">
         <v>45689</v>
       </c>
       <c r="C163" t="s">
@@ -33828,7 +33836,7 @@
       <c r="A164" t="s">
         <v>62</v>
       </c>
-      <c r="B164">
+      <c r="B164" s="5">
         <v>45717</v>
       </c>
       <c r="C164" t="s">
@@ -33944,7 +33952,7 @@
       <c r="A165" t="s">
         <v>62</v>
       </c>
-      <c r="B165">
+      <c r="B165" s="5">
         <v>45748</v>
       </c>
       <c r="C165" t="s">
@@ -34060,7 +34068,7 @@
       <c r="A166" t="s">
         <v>63</v>
       </c>
-      <c r="B166">
+      <c r="B166" s="5">
         <v>45658</v>
       </c>
       <c r="C166" t="s">
@@ -34176,7 +34184,7 @@
       <c r="A167" t="s">
         <v>63</v>
       </c>
-      <c r="B167">
+      <c r="B167" s="5">
         <v>45689</v>
       </c>
       <c r="C167" t="s">
@@ -34292,7 +34300,7 @@
       <c r="A168" t="s">
         <v>63</v>
       </c>
-      <c r="B168">
+      <c r="B168" s="5">
         <v>45717</v>
       </c>
       <c r="C168" t="s">
@@ -34408,7 +34416,7 @@
       <c r="A169" t="s">
         <v>63</v>
       </c>
-      <c r="B169">
+      <c r="B169" s="5">
         <v>45748</v>
       </c>
       <c r="C169" t="s">
@@ -34524,7 +34532,7 @@
       <c r="A170" t="s">
         <v>64</v>
       </c>
-      <c r="B170">
+      <c r="B170" s="5">
         <v>45658</v>
       </c>
       <c r="C170" t="s">
@@ -34640,7 +34648,7 @@
       <c r="A171" t="s">
         <v>64</v>
       </c>
-      <c r="B171">
+      <c r="B171" s="5">
         <v>45689</v>
       </c>
       <c r="C171" t="s">
@@ -34756,7 +34764,7 @@
       <c r="A172" t="s">
         <v>64</v>
       </c>
-      <c r="B172">
+      <c r="B172" s="5">
         <v>45717</v>
       </c>
       <c r="C172" t="s">
@@ -34872,7 +34880,7 @@
       <c r="A173" t="s">
         <v>64</v>
       </c>
-      <c r="B173">
+      <c r="B173" s="5">
         <v>45748</v>
       </c>
       <c r="C173" t="s">
@@ -34988,7 +34996,7 @@
       <c r="A174" t="s">
         <v>65</v>
       </c>
-      <c r="B174">
+      <c r="B174" s="5">
         <v>45658</v>
       </c>
       <c r="C174" t="s">
@@ -35104,7 +35112,7 @@
       <c r="A175" t="s">
         <v>65</v>
       </c>
-      <c r="B175">
+      <c r="B175" s="5">
         <v>45689</v>
       </c>
       <c r="C175" t="s">
@@ -35220,7 +35228,7 @@
       <c r="A176" t="s">
         <v>65</v>
       </c>
-      <c r="B176">
+      <c r="B176" s="5">
         <v>45717</v>
       </c>
       <c r="C176" t="s">
@@ -35336,7 +35344,7 @@
       <c r="A177" t="s">
         <v>65</v>
       </c>
-      <c r="B177">
+      <c r="B177" s="5">
         <v>45748</v>
       </c>
       <c r="C177" t="s">
@@ -35452,7 +35460,7 @@
       <c r="A178" t="s">
         <v>66</v>
       </c>
-      <c r="B178">
+      <c r="B178" s="5">
         <v>45658</v>
       </c>
       <c r="C178" t="s">
@@ -35568,7 +35576,7 @@
       <c r="A179" t="s">
         <v>66</v>
       </c>
-      <c r="B179">
+      <c r="B179" s="5">
         <v>45689</v>
       </c>
       <c r="C179" t="s">
@@ -35684,7 +35692,7 @@
       <c r="A180" t="s">
         <v>66</v>
       </c>
-      <c r="B180">
+      <c r="B180" s="5">
         <v>45717</v>
       </c>
       <c r="C180" t="s">
@@ -35800,7 +35808,7 @@
       <c r="A181" t="s">
         <v>66</v>
       </c>
-      <c r="B181">
+      <c r="B181" s="5">
         <v>45748</v>
       </c>
       <c r="C181" t="s">
@@ -35916,7 +35924,7 @@
       <c r="A182" t="s">
         <v>67</v>
       </c>
-      <c r="B182">
+      <c r="B182" s="5">
         <v>45658</v>
       </c>
       <c r="C182" t="s">
@@ -36032,7 +36040,7 @@
       <c r="A183" t="s">
         <v>67</v>
       </c>
-      <c r="B183">
+      <c r="B183" s="5">
         <v>45689</v>
       </c>
       <c r="C183" t="s">
@@ -36148,7 +36156,7 @@
       <c r="A184" t="s">
         <v>67</v>
       </c>
-      <c r="B184">
+      <c r="B184" s="5">
         <v>45717</v>
       </c>
       <c r="C184" t="s">
@@ -36264,7 +36272,7 @@
       <c r="A185" t="s">
         <v>67</v>
       </c>
-      <c r="B185">
+      <c r="B185" s="5">
         <v>45748</v>
       </c>
       <c r="C185" t="s">
@@ -36380,7 +36388,7 @@
       <c r="A186" t="s">
         <v>68</v>
       </c>
-      <c r="B186">
+      <c r="B186" s="5">
         <v>45658</v>
       </c>
       <c r="C186" t="s">
@@ -36496,7 +36504,7 @@
       <c r="A187" t="s">
         <v>68</v>
       </c>
-      <c r="B187">
+      <c r="B187" s="5">
         <v>45689</v>
       </c>
       <c r="C187" t="s">
@@ -36612,7 +36620,7 @@
       <c r="A188" t="s">
         <v>68</v>
       </c>
-      <c r="B188">
+      <c r="B188" s="5">
         <v>45717</v>
       </c>
       <c r="C188" t="s">
@@ -36728,7 +36736,7 @@
       <c r="A189" t="s">
         <v>68</v>
       </c>
-      <c r="B189">
+      <c r="B189" s="5">
         <v>45748</v>
       </c>
       <c r="C189" t="s">
@@ -36844,7 +36852,7 @@
       <c r="A190" t="s">
         <v>69</v>
       </c>
-      <c r="B190">
+      <c r="B190" s="5">
         <v>45658</v>
       </c>
       <c r="C190" t="s">
@@ -36960,7 +36968,7 @@
       <c r="A191" t="s">
         <v>69</v>
       </c>
-      <c r="B191">
+      <c r="B191" s="5">
         <v>45689</v>
       </c>
       <c r="C191" t="s">
@@ -37076,7 +37084,7 @@
       <c r="A192" t="s">
         <v>69</v>
       </c>
-      <c r="B192">
+      <c r="B192" s="5">
         <v>45717</v>
       </c>
       <c r="C192" t="s">
@@ -37192,7 +37200,7 @@
       <c r="A193" t="s">
         <v>69</v>
       </c>
-      <c r="B193">
+      <c r="B193" s="5">
         <v>45748</v>
       </c>
       <c r="C193" t="s">
@@ -37308,7 +37316,7 @@
       <c r="A194" t="s">
         <v>70</v>
       </c>
-      <c r="B194">
+      <c r="B194" s="5">
         <v>45658</v>
       </c>
       <c r="C194" t="s">
@@ -37424,7 +37432,7 @@
       <c r="A195" t="s">
         <v>70</v>
       </c>
-      <c r="B195">
+      <c r="B195" s="5">
         <v>45689</v>
       </c>
       <c r="C195" t="s">
@@ -37540,7 +37548,7 @@
       <c r="A196" t="s">
         <v>70</v>
       </c>
-      <c r="B196">
+      <c r="B196" s="5">
         <v>45717</v>
       </c>
       <c r="C196" t="s">
@@ -37656,7 +37664,7 @@
       <c r="A197" t="s">
         <v>70</v>
       </c>
-      <c r="B197">
+      <c r="B197" s="5">
         <v>45748</v>
       </c>
       <c r="C197" t="s">
@@ -37772,7 +37780,7 @@
       <c r="A198" t="s">
         <v>71</v>
       </c>
-      <c r="B198">
+      <c r="B198" s="5">
         <v>45658</v>
       </c>
       <c r="C198" t="s">
@@ -37888,7 +37896,7 @@
       <c r="A199" t="s">
         <v>71</v>
       </c>
-      <c r="B199">
+      <c r="B199" s="5">
         <v>45689</v>
       </c>
       <c r="C199" t="s">
@@ -38004,7 +38012,7 @@
       <c r="A200" t="s">
         <v>71</v>
       </c>
-      <c r="B200">
+      <c r="B200" s="5">
         <v>45717</v>
       </c>
       <c r="C200" t="s">
@@ -38120,7 +38128,7 @@
       <c r="A201" t="s">
         <v>71</v>
       </c>
-      <c r="B201">
+      <c r="B201" s="5">
         <v>45748</v>
       </c>
       <c r="C201" t="s">
@@ -38236,7 +38244,7 @@
       <c r="A202" t="s">
         <v>72</v>
       </c>
-      <c r="B202">
+      <c r="B202" s="5">
         <v>45658</v>
       </c>
       <c r="C202" t="s">
@@ -38352,7 +38360,7 @@
       <c r="A203" t="s">
         <v>72</v>
       </c>
-      <c r="B203">
+      <c r="B203" s="5">
         <v>45689</v>
       </c>
       <c r="C203" t="s">
@@ -38468,7 +38476,7 @@
       <c r="A204" t="s">
         <v>72</v>
       </c>
-      <c r="B204">
+      <c r="B204" s="5">
         <v>45717</v>
       </c>
       <c r="C204" t="s">
@@ -38584,7 +38592,7 @@
       <c r="A205" t="s">
         <v>72</v>
       </c>
-      <c r="B205">
+      <c r="B205" s="5">
         <v>45748</v>
       </c>
       <c r="C205" t="s">
@@ -38700,7 +38708,7 @@
       <c r="A206" t="s">
         <v>73</v>
       </c>
-      <c r="B206">
+      <c r="B206" s="5">
         <v>45658</v>
       </c>
       <c r="C206" t="s">
@@ -38816,7 +38824,7 @@
       <c r="A207" t="s">
         <v>73</v>
       </c>
-      <c r="B207">
+      <c r="B207" s="5">
         <v>45689</v>
       </c>
       <c r="C207" t="s">
@@ -38932,7 +38940,7 @@
       <c r="A208" t="s">
         <v>73</v>
       </c>
-      <c r="B208">
+      <c r="B208" s="5">
         <v>45717</v>
       </c>
       <c r="C208" t="s">
@@ -39048,7 +39056,7 @@
       <c r="A209" t="s">
         <v>73</v>
       </c>
-      <c r="B209">
+      <c r="B209" s="5">
         <v>45748</v>
       </c>
       <c r="C209" t="s">
@@ -39164,7 +39172,7 @@
       <c r="A210" t="s">
         <v>74</v>
       </c>
-      <c r="B210">
+      <c r="B210" s="5">
         <v>45658</v>
       </c>
       <c r="C210" t="s">
@@ -39280,7 +39288,7 @@
       <c r="A211" t="s">
         <v>74</v>
       </c>
-      <c r="B211">
+      <c r="B211" s="5">
         <v>45689</v>
       </c>
       <c r="C211" t="s">
@@ -39396,7 +39404,7 @@
       <c r="A212" t="s">
         <v>74</v>
       </c>
-      <c r="B212">
+      <c r="B212" s="5">
         <v>45717</v>
       </c>
       <c r="C212" t="s">
@@ -39512,7 +39520,7 @@
       <c r="A213" t="s">
         <v>74</v>
       </c>
-      <c r="B213">
+      <c r="B213" s="5">
         <v>45748</v>
       </c>
       <c r="C213" t="s">
@@ -39628,7 +39636,7 @@
       <c r="A214" t="s">
         <v>75</v>
       </c>
-      <c r="B214">
+      <c r="B214" s="5">
         <v>45658</v>
       </c>
       <c r="C214" t="s">
@@ -39744,7 +39752,7 @@
       <c r="A215" t="s">
         <v>75</v>
       </c>
-      <c r="B215">
+      <c r="B215" s="5">
         <v>45689</v>
       </c>
       <c r="C215" t="s">
@@ -39860,7 +39868,7 @@
       <c r="A216" t="s">
         <v>75</v>
       </c>
-      <c r="B216">
+      <c r="B216" s="5">
         <v>45717</v>
       </c>
       <c r="C216" t="s">
@@ -39976,7 +39984,7 @@
       <c r="A217" t="s">
         <v>75</v>
       </c>
-      <c r="B217">
+      <c r="B217" s="5">
         <v>45748</v>
       </c>
       <c r="C217" t="s">
@@ -40092,7 +40100,7 @@
       <c r="A218" t="s">
         <v>76</v>
       </c>
-      <c r="B218">
+      <c r="B218" s="5">
         <v>45658</v>
       </c>
       <c r="C218" t="s">
@@ -40208,7 +40216,7 @@
       <c r="A219" t="s">
         <v>76</v>
       </c>
-      <c r="B219">
+      <c r="B219" s="5">
         <v>45689</v>
       </c>
       <c r="C219" t="s">
@@ -40324,7 +40332,7 @@
       <c r="A220" t="s">
         <v>76</v>
       </c>
-      <c r="B220">
+      <c r="B220" s="5">
         <v>45717</v>
       </c>
       <c r="C220" t="s">
@@ -40440,7 +40448,7 @@
       <c r="A221" t="s">
         <v>76</v>
       </c>
-      <c r="B221">
+      <c r="B221" s="5">
         <v>45748</v>
       </c>
       <c r="C221" t="s">
@@ -40556,7 +40564,7 @@
       <c r="A222" t="s">
         <v>77</v>
       </c>
-      <c r="B222">
+      <c r="B222" s="5">
         <v>45658</v>
       </c>
       <c r="C222" t="s">
@@ -40672,7 +40680,7 @@
       <c r="A223" t="s">
         <v>77</v>
       </c>
-      <c r="B223">
+      <c r="B223" s="5">
         <v>45689</v>
       </c>
       <c r="C223" t="s">
@@ -40788,7 +40796,7 @@
       <c r="A224" t="s">
         <v>77</v>
       </c>
-      <c r="B224">
+      <c r="B224" s="5">
         <v>45717</v>
       </c>
       <c r="C224" t="s">
@@ -40904,7 +40912,7 @@
       <c r="A225" t="s">
         <v>77</v>
       </c>
-      <c r="B225">
+      <c r="B225" s="5">
         <v>45748</v>
       </c>
       <c r="C225" t="s">
@@ -41020,7 +41028,7 @@
       <c r="A226" t="s">
         <v>78</v>
       </c>
-      <c r="B226">
+      <c r="B226" s="5">
         <v>45658</v>
       </c>
       <c r="C226" t="s">
@@ -41136,7 +41144,7 @@
       <c r="A227" t="s">
         <v>78</v>
       </c>
-      <c r="B227">
+      <c r="B227" s="5">
         <v>45689</v>
       </c>
       <c r="C227" t="s">
@@ -41252,7 +41260,7 @@
       <c r="A228" t="s">
         <v>78</v>
       </c>
-      <c r="B228">
+      <c r="B228" s="5">
         <v>45717</v>
       </c>
       <c r="C228" t="s">
@@ -41368,7 +41376,7 @@
       <c r="A229" t="s">
         <v>78</v>
       </c>
-      <c r="B229">
+      <c r="B229" s="5">
         <v>45748</v>
       </c>
       <c r="C229" t="s">
@@ -41484,7 +41492,7 @@
       <c r="A230" t="s">
         <v>79</v>
       </c>
-      <c r="B230">
+      <c r="B230" s="5">
         <v>45658</v>
       </c>
       <c r="C230" t="s">
@@ -41600,7 +41608,7 @@
       <c r="A231" t="s">
         <v>79</v>
       </c>
-      <c r="B231">
+      <c r="B231" s="5">
         <v>45689</v>
       </c>
       <c r="C231" t="s">
@@ -41716,7 +41724,7 @@
       <c r="A232" t="s">
         <v>79</v>
       </c>
-      <c r="B232">
+      <c r="B232" s="5">
         <v>45717</v>
       </c>
       <c r="C232" t="s">
@@ -41832,7 +41840,7 @@
       <c r="A233" t="s">
         <v>79</v>
       </c>
-      <c r="B233">
+      <c r="B233" s="5">
         <v>45748</v>
       </c>
       <c r="C233" t="s">
@@ -41948,7 +41956,7 @@
       <c r="A234" t="s">
         <v>80</v>
       </c>
-      <c r="B234">
+      <c r="B234" s="5">
         <v>45658</v>
       </c>
       <c r="C234" t="s">
@@ -42064,7 +42072,7 @@
       <c r="A235" t="s">
         <v>80</v>
       </c>
-      <c r="B235">
+      <c r="B235" s="5">
         <v>45689</v>
       </c>
       <c r="C235" t="s">
@@ -42180,7 +42188,7 @@
       <c r="A236" t="s">
         <v>80</v>
       </c>
-      <c r="B236">
+      <c r="B236" s="5">
         <v>45717</v>
       </c>
       <c r="C236" t="s">
@@ -42296,7 +42304,7 @@
       <c r="A237" t="s">
         <v>80</v>
       </c>
-      <c r="B237">
+      <c r="B237" s="5">
         <v>45748</v>
       </c>
       <c r="C237" t="s">
@@ -42412,7 +42420,7 @@
       <c r="A238" t="s">
         <v>81</v>
       </c>
-      <c r="B238">
+      <c r="B238" s="5">
         <v>45658</v>
       </c>
       <c r="C238" t="s">
@@ -42528,7 +42536,7 @@
       <c r="A239" t="s">
         <v>81</v>
       </c>
-      <c r="B239">
+      <c r="B239" s="5">
         <v>45689</v>
       </c>
       <c r="C239" t="s">
@@ -42644,7 +42652,7 @@
       <c r="A240" t="s">
         <v>81</v>
       </c>
-      <c r="B240">
+      <c r="B240" s="5">
         <v>45717</v>
       </c>
       <c r="C240" t="s">
@@ -42760,7 +42768,7 @@
       <c r="A241" t="s">
         <v>81</v>
       </c>
-      <c r="B241">
+      <c r="B241" s="5">
         <v>45748</v>
       </c>
       <c r="C241" t="s">
@@ -42876,7 +42884,7 @@
       <c r="A242" t="s">
         <v>82</v>
       </c>
-      <c r="B242">
+      <c r="B242" s="5">
         <v>45658</v>
       </c>
       <c r="C242" t="s">
@@ -42992,7 +43000,7 @@
       <c r="A243" t="s">
         <v>82</v>
       </c>
-      <c r="B243">
+      <c r="B243" s="5">
         <v>45689</v>
       </c>
       <c r="C243" t="s">
@@ -43108,7 +43116,7 @@
       <c r="A244" t="s">
         <v>82</v>
       </c>
-      <c r="B244">
+      <c r="B244" s="5">
         <v>45717</v>
       </c>
       <c r="C244" t="s">
@@ -43224,7 +43232,7 @@
       <c r="A245" t="s">
         <v>82</v>
       </c>
-      <c r="B245">
+      <c r="B245" s="5">
         <v>45748</v>
       </c>
       <c r="C245" t="s">
@@ -43340,7 +43348,7 @@
       <c r="A246" t="s">
         <v>83</v>
       </c>
-      <c r="B246">
+      <c r="B246" s="5">
         <v>45658</v>
       </c>
       <c r="C246" t="s">
@@ -43456,7 +43464,7 @@
       <c r="A247" t="s">
         <v>83</v>
       </c>
-      <c r="B247">
+      <c r="B247" s="5">
         <v>45689</v>
       </c>
       <c r="C247" t="s">
@@ -43572,7 +43580,7 @@
       <c r="A248" t="s">
         <v>83</v>
       </c>
-      <c r="B248">
+      <c r="B248" s="5">
         <v>45717</v>
       </c>
       <c r="C248" t="s">
@@ -43688,7 +43696,7 @@
       <c r="A249" t="s">
         <v>83</v>
       </c>
-      <c r="B249">
+      <c r="B249" s="5">
         <v>45748</v>
       </c>
       <c r="C249" t="s">
@@ -43804,7 +43812,7 @@
       <c r="A250" t="s">
         <v>84</v>
       </c>
-      <c r="B250">
+      <c r="B250" s="5">
         <v>45658</v>
       </c>
       <c r="C250" t="s">
@@ -43920,7 +43928,7 @@
       <c r="A251" t="s">
         <v>84</v>
       </c>
-      <c r="B251">
+      <c r="B251" s="5">
         <v>45689</v>
       </c>
       <c r="C251" t="s">
@@ -44036,7 +44044,7 @@
       <c r="A252" t="s">
         <v>84</v>
       </c>
-      <c r="B252">
+      <c r="B252" s="5">
         <v>45717</v>
       </c>
       <c r="C252" t="s">
@@ -44152,7 +44160,7 @@
       <c r="A253" t="s">
         <v>84</v>
       </c>
-      <c r="B253">
+      <c r="B253" s="5">
         <v>45748</v>
       </c>
       <c r="C253" t="s">
@@ -44268,7 +44276,7 @@
       <c r="A254" t="s">
         <v>85</v>
       </c>
-      <c r="B254">
+      <c r="B254" s="5">
         <v>45658</v>
       </c>
       <c r="C254" t="s">
@@ -44384,7 +44392,7 @@
       <c r="A255" t="s">
         <v>85</v>
       </c>
-      <c r="B255">
+      <c r="B255" s="5">
         <v>45689</v>
       </c>
       <c r="C255" t="s">
@@ -44500,7 +44508,7 @@
       <c r="A256" t="s">
         <v>85</v>
       </c>
-      <c r="B256">
+      <c r="B256" s="5">
         <v>45717</v>
       </c>
       <c r="C256" t="s">
@@ -44616,7 +44624,7 @@
       <c r="A257" t="s">
         <v>85</v>
       </c>
-      <c r="B257">
+      <c r="B257" s="5">
         <v>45748</v>
       </c>
       <c r="C257" t="s">
@@ -44732,7 +44740,7 @@
       <c r="A258" t="s">
         <v>86</v>
       </c>
-      <c r="B258">
+      <c r="B258" s="5">
         <v>45658</v>
       </c>
       <c r="C258" t="s">
@@ -44848,7 +44856,7 @@
       <c r="A259" t="s">
         <v>86</v>
       </c>
-      <c r="B259">
+      <c r="B259" s="5">
         <v>45689</v>
       </c>
       <c r="C259" t="s">
@@ -44964,7 +44972,7 @@
       <c r="A260" t="s">
         <v>86</v>
       </c>
-      <c r="B260">
+      <c r="B260" s="5">
         <v>45717</v>
       </c>
       <c r="C260" t="s">
@@ -45080,7 +45088,7 @@
       <c r="A261" t="s">
         <v>86</v>
       </c>
-      <c r="B261">
+      <c r="B261" s="5">
         <v>45748</v>
       </c>
       <c r="C261" t="s">
@@ -45196,7 +45204,7 @@
       <c r="A262" t="s">
         <v>87</v>
       </c>
-      <c r="B262">
+      <c r="B262" s="5">
         <v>45658</v>
       </c>
       <c r="C262" t="s">
@@ -45312,7 +45320,7 @@
       <c r="A263" t="s">
         <v>87</v>
       </c>
-      <c r="B263">
+      <c r="B263" s="5">
         <v>45689</v>
       </c>
       <c r="C263" t="s">
@@ -45428,7 +45436,7 @@
       <c r="A264" t="s">
         <v>87</v>
       </c>
-      <c r="B264">
+      <c r="B264" s="5">
         <v>45717</v>
       </c>
       <c r="C264" t="s">
@@ -45544,7 +45552,7 @@
       <c r="A265" t="s">
         <v>87</v>
       </c>
-      <c r="B265">
+      <c r="B265" s="5">
         <v>45748</v>
       </c>
       <c r="C265" t="s">
@@ -45660,7 +45668,7 @@
       <c r="A266" t="s">
         <v>88</v>
       </c>
-      <c r="B266">
+      <c r="B266" s="5">
         <v>45658</v>
       </c>
       <c r="C266" t="s">
@@ -45776,7 +45784,7 @@
       <c r="A267" t="s">
         <v>88</v>
       </c>
-      <c r="B267">
+      <c r="B267" s="5">
         <v>45689</v>
       </c>
       <c r="C267" t="s">
@@ -45892,7 +45900,7 @@
       <c r="A268" t="s">
         <v>88</v>
       </c>
-      <c r="B268">
+      <c r="B268" s="5">
         <v>45717</v>
       </c>
       <c r="C268" t="s">
@@ -46008,7 +46016,7 @@
       <c r="A269" t="s">
         <v>88</v>
       </c>
-      <c r="B269">
+      <c r="B269" s="5">
         <v>45748</v>
       </c>
       <c r="C269" t="s">
@@ -46124,7 +46132,7 @@
       <c r="A270" t="s">
         <v>89</v>
       </c>
-      <c r="B270">
+      <c r="B270" s="5">
         <v>45658</v>
       </c>
       <c r="C270" t="s">
@@ -46240,7 +46248,7 @@
       <c r="A271" t="s">
         <v>89</v>
       </c>
-      <c r="B271">
+      <c r="B271" s="5">
         <v>45689</v>
       </c>
       <c r="C271" t="s">
@@ -46356,7 +46364,7 @@
       <c r="A272" t="s">
         <v>89</v>
       </c>
-      <c r="B272">
+      <c r="B272" s="5">
         <v>45717</v>
       </c>
       <c r="C272" t="s">
@@ -46472,7 +46480,7 @@
       <c r="A273" t="s">
         <v>89</v>
       </c>
-      <c r="B273">
+      <c r="B273" s="5">
         <v>45748</v>
       </c>
       <c r="C273" t="s">
@@ -46588,7 +46596,7 @@
       <c r="A274" t="s">
         <v>90</v>
       </c>
-      <c r="B274">
+      <c r="B274" s="5">
         <v>45658</v>
       </c>
       <c r="C274" t="s">
@@ -46704,7 +46712,7 @@
       <c r="A275" t="s">
         <v>90</v>
       </c>
-      <c r="B275">
+      <c r="B275" s="5">
         <v>45689</v>
       </c>
       <c r="C275" t="s">
@@ -46820,7 +46828,7 @@
       <c r="A276" t="s">
         <v>90</v>
       </c>
-      <c r="B276">
+      <c r="B276" s="5">
         <v>45717</v>
       </c>
       <c r="C276" t="s">
@@ -46936,7 +46944,7 @@
       <c r="A277" t="s">
         <v>90</v>
       </c>
-      <c r="B277">
+      <c r="B277" s="5">
         <v>45748</v>
       </c>
       <c r="C277" t="s">
@@ -47052,7 +47060,7 @@
       <c r="A278" t="s">
         <v>91</v>
       </c>
-      <c r="B278">
+      <c r="B278" s="5">
         <v>45658</v>
       </c>
       <c r="C278" t="s">
@@ -47168,7 +47176,7 @@
       <c r="A279" t="s">
         <v>91</v>
       </c>
-      <c r="B279">
+      <c r="B279" s="5">
         <v>45689</v>
       </c>
       <c r="C279" t="s">
@@ -47284,7 +47292,7 @@
       <c r="A280" t="s">
         <v>91</v>
       </c>
-      <c r="B280">
+      <c r="B280" s="5">
         <v>45717</v>
       </c>
       <c r="C280" t="s">
@@ -47400,7 +47408,7 @@
       <c r="A281" t="s">
         <v>91</v>
       </c>
-      <c r="B281">
+      <c r="B281" s="5">
         <v>45748</v>
       </c>
       <c r="C281" t="s">
@@ -47516,7 +47524,7 @@
       <c r="A282" t="s">
         <v>92</v>
       </c>
-      <c r="B282">
+      <c r="B282" s="5">
         <v>45658</v>
       </c>
       <c r="C282" t="s">
@@ -47632,7 +47640,7 @@
       <c r="A283" t="s">
         <v>92</v>
       </c>
-      <c r="B283">
+      <c r="B283" s="5">
         <v>45689</v>
       </c>
       <c r="C283" t="s">
@@ -47748,7 +47756,7 @@
       <c r="A284" t="s">
         <v>92</v>
       </c>
-      <c r="B284">
+      <c r="B284" s="5">
         <v>45717</v>
       </c>
       <c r="C284" t="s">
@@ -47864,7 +47872,7 @@
       <c r="A285" t="s">
         <v>92</v>
       </c>
-      <c r="B285">
+      <c r="B285" s="5">
         <v>45748</v>
       </c>
       <c r="C285" t="s">
@@ -47980,7 +47988,7 @@
       <c r="A286" t="s">
         <v>93</v>
       </c>
-      <c r="B286">
+      <c r="B286" s="5">
         <v>45658</v>
       </c>
       <c r="C286" t="s">
@@ -48096,7 +48104,7 @@
       <c r="A287" t="s">
         <v>93</v>
       </c>
-      <c r="B287">
+      <c r="B287" s="5">
         <v>45689</v>
       </c>
       <c r="C287" t="s">
@@ -48212,7 +48220,7 @@
       <c r="A288" t="s">
         <v>93</v>
       </c>
-      <c r="B288">
+      <c r="B288" s="5">
         <v>45717</v>
       </c>
       <c r="C288" t="s">
@@ -48328,7 +48336,7 @@
       <c r="A289" t="s">
         <v>93</v>
       </c>
-      <c r="B289">
+      <c r="B289" s="5">
         <v>45748</v>
       </c>
       <c r="C289" t="s">
@@ -48444,7 +48452,7 @@
       <c r="A290" t="s">
         <v>94</v>
       </c>
-      <c r="B290">
+      <c r="B290" s="5">
         <v>45658</v>
       </c>
       <c r="C290" t="s">
@@ -48560,7 +48568,7 @@
       <c r="A291" t="s">
         <v>94</v>
       </c>
-      <c r="B291">
+      <c r="B291" s="5">
         <v>45689</v>
       </c>
       <c r="C291" t="s">
@@ -48676,7 +48684,7 @@
       <c r="A292" t="s">
         <v>94</v>
       </c>
-      <c r="B292">
+      <c r="B292" s="5">
         <v>45717</v>
       </c>
       <c r="C292" t="s">
@@ -48792,7 +48800,7 @@
       <c r="A293" t="s">
         <v>94</v>
       </c>
-      <c r="B293">
+      <c r="B293" s="5">
         <v>45748</v>
       </c>
       <c r="C293" t="s">
@@ -48908,7 +48916,7 @@
       <c r="A294" t="s">
         <v>95</v>
       </c>
-      <c r="B294">
+      <c r="B294" s="5">
         <v>45658</v>
       </c>
       <c r="C294" t="s">
@@ -49024,7 +49032,7 @@
       <c r="A295" t="s">
         <v>95</v>
       </c>
-      <c r="B295">
+      <c r="B295" s="5">
         <v>45689</v>
       </c>
       <c r="C295" t="s">
@@ -49140,7 +49148,7 @@
       <c r="A296" t="s">
         <v>95</v>
       </c>
-      <c r="B296">
+      <c r="B296" s="5">
         <v>45717</v>
       </c>
       <c r="C296" t="s">
@@ -49256,7 +49264,7 @@
       <c r="A297" t="s">
         <v>95</v>
       </c>
-      <c r="B297">
+      <c r="B297" s="5">
         <v>45748</v>
       </c>
       <c r="C297" t="s">
@@ -49372,7 +49380,7 @@
       <c r="A298" t="s">
         <v>96</v>
       </c>
-      <c r="B298">
+      <c r="B298" s="5">
         <v>45658</v>
       </c>
       <c r="C298" t="s">
@@ -49488,7 +49496,7 @@
       <c r="A299" t="s">
         <v>96</v>
       </c>
-      <c r="B299">
+      <c r="B299" s="5">
         <v>45689</v>
       </c>
       <c r="C299" t="s">
@@ -49604,7 +49612,7 @@
       <c r="A300" t="s">
         <v>96</v>
       </c>
-      <c r="B300">
+      <c r="B300" s="5">
         <v>45717</v>
       </c>
       <c r="C300" t="s">
@@ -49720,7 +49728,7 @@
       <c r="A301" t="s">
         <v>96</v>
       </c>
-      <c r="B301">
+      <c r="B301" s="5">
         <v>45748</v>
       </c>
       <c r="C301" t="s">
@@ -49836,7 +49844,7 @@
       <c r="A302" t="s">
         <v>97</v>
       </c>
-      <c r="B302">
+      <c r="B302" s="5">
         <v>45658</v>
       </c>
       <c r="C302" t="s">
@@ -49952,7 +49960,7 @@
       <c r="A303" t="s">
         <v>97</v>
       </c>
-      <c r="B303">
+      <c r="B303" s="5">
         <v>45689</v>
       </c>
       <c r="C303" t="s">
@@ -50068,7 +50076,7 @@
       <c r="A304" t="s">
         <v>97</v>
       </c>
-      <c r="B304">
+      <c r="B304" s="5">
         <v>45717</v>
       </c>
       <c r="C304" t="s">
@@ -50184,7 +50192,7 @@
       <c r="A305" t="s">
         <v>97</v>
       </c>
-      <c r="B305">
+      <c r="B305" s="5">
         <v>45748</v>
       </c>
       <c r="C305" t="s">
@@ -50300,7 +50308,7 @@
       <c r="A306" t="s">
         <v>98</v>
       </c>
-      <c r="B306">
+      <c r="B306" s="5">
         <v>45658</v>
       </c>
       <c r="C306" t="s">
@@ -50416,7 +50424,7 @@
       <c r="A307" t="s">
         <v>98</v>
       </c>
-      <c r="B307">
+      <c r="B307" s="5">
         <v>45689</v>
       </c>
       <c r="C307" t="s">
@@ -50532,7 +50540,7 @@
       <c r="A308" t="s">
         <v>98</v>
       </c>
-      <c r="B308">
+      <c r="B308" s="5">
         <v>45717</v>
       </c>
       <c r="C308" t="s">
@@ -50648,7 +50656,7 @@
       <c r="A309" t="s">
         <v>98</v>
       </c>
-      <c r="B309">
+      <c r="B309" s="5">
         <v>45748</v>
       </c>
       <c r="C309" t="s">
@@ -50764,7 +50772,7 @@
       <c r="A310" t="s">
         <v>99</v>
       </c>
-      <c r="B310">
+      <c r="B310" s="5">
         <v>45658</v>
       </c>
       <c r="C310" t="s">
@@ -50880,7 +50888,7 @@
       <c r="A311" t="s">
         <v>99</v>
       </c>
-      <c r="B311">
+      <c r="B311" s="5">
         <v>45689</v>
       </c>
       <c r="C311" t="s">
@@ -50996,7 +51004,7 @@
       <c r="A312" t="s">
         <v>99</v>
       </c>
-      <c r="B312">
+      <c r="B312" s="5">
         <v>45717</v>
       </c>
       <c r="C312" t="s">
@@ -51112,7 +51120,7 @@
       <c r="A313" t="s">
         <v>99</v>
       </c>
-      <c r="B313">
+      <c r="B313" s="5">
         <v>45748</v>
       </c>
       <c r="C313" t="s">
@@ -51228,7 +51236,7 @@
       <c r="A314" t="s">
         <v>100</v>
       </c>
-      <c r="B314">
+      <c r="B314" s="5">
         <v>45658</v>
       </c>
       <c r="C314" t="s">
@@ -51344,7 +51352,7 @@
       <c r="A315" t="s">
         <v>100</v>
       </c>
-      <c r="B315">
+      <c r="B315" s="5">
         <v>45689</v>
       </c>
       <c r="C315" t="s">
@@ -51460,7 +51468,7 @@
       <c r="A316" t="s">
         <v>100</v>
       </c>
-      <c r="B316">
+      <c r="B316" s="5">
         <v>45717</v>
       </c>
       <c r="C316" t="s">
@@ -51576,7 +51584,7 @@
       <c r="A317" t="s">
         <v>100</v>
       </c>
-      <c r="B317">
+      <c r="B317" s="5">
         <v>45748</v>
       </c>
       <c r="C317" t="s">
@@ -51692,7 +51700,7 @@
       <c r="A318" t="s">
         <v>101</v>
       </c>
-      <c r="B318">
+      <c r="B318" s="5">
         <v>45658</v>
       </c>
       <c r="C318" t="s">
@@ -51808,7 +51816,7 @@
       <c r="A319" t="s">
         <v>101</v>
       </c>
-      <c r="B319">
+      <c r="B319" s="5">
         <v>45689</v>
       </c>
       <c r="C319" t="s">
@@ -51924,7 +51932,7 @@
       <c r="A320" t="s">
         <v>101</v>
       </c>
-      <c r="B320">
+      <c r="B320" s="5">
         <v>45717</v>
       </c>
       <c r="C320" t="s">
@@ -52040,7 +52048,7 @@
       <c r="A321" t="s">
         <v>101</v>
       </c>
-      <c r="B321">
+      <c r="B321" s="5">
         <v>45748</v>
       </c>
       <c r="C321" t="s">
@@ -64396,82 +64404,82 @@
     </row>
     <row r="2" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="R3" s="5" t="s">
+      <c r="B3" s="4"/>
+      <c r="R3" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="S3" s="5"/>
+      <c r="S3" s="4"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4">
         <v>0.85807070804410468</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="R4" t="s">
         <v>110</v>
       </c>
-      <c r="S4" s="2">
+      <c r="S4">
         <v>0.40895561021322352</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>111</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5">
         <v>0.73628534000331114</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="R5" t="s">
         <v>111</v>
       </c>
-      <c r="S5" s="2">
+      <c r="S5">
         <v>0.16724469112487</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>112</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6">
         <v>0.73545604861967373</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="R6" t="s">
         <v>112</v>
       </c>
-      <c r="S6" s="2">
+      <c r="S6">
         <v>0.16462596373847024</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7">
         <v>53373.736380790499</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="R7" t="s">
         <v>113</v>
       </c>
-      <c r="S7" s="2">
+      <c r="S7">
         <v>94846.03383215853</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>320</v>
       </c>
-      <c r="R8" s="3" t="s">
+      <c r="R8" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="S8" s="3">
+      <c r="S8" s="2">
         <v>320</v>
       </c>
     </row>
@@ -64484,295 +64492,291 @@
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4" t="s">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4" t="s">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="T11" s="4" t="s">
+      <c r="T11" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="U11" s="4" t="s">
+      <c r="U11" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="V11" s="4" t="s">
+      <c r="V11" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="W11" s="4" t="s">
+      <c r="W11" s="3" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" t="s">
         <v>116</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12">
         <v>2529264292982.4736</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12">
         <v>2529264292982.4736</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12">
         <v>887.84877611276033</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12">
         <v>4.7503615090053331E-94</v>
       </c>
-      <c r="R12" s="2" t="s">
+      <c r="R12" t="s">
         <v>116</v>
       </c>
-      <c r="S12" s="2">
+      <c r="S12">
         <v>1</v>
       </c>
-      <c r="T12" s="2">
+      <c r="T12">
         <v>574513714277.01416</v>
       </c>
-      <c r="U12" s="2">
+      <c r="U12">
         <v>574513714277.01416</v>
       </c>
-      <c r="V12" s="2">
+      <c r="V12">
         <v>63.864872683367629</v>
       </c>
-      <c r="W12" s="2">
+      <c r="W12">
         <v>2.4800615101359619E-14</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" t="s">
         <v>117</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13">
         <v>318</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13">
         <v>905904323808.26587</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13">
         <v>2848755735.246119</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="R13" s="2" t="s">
+      <c r="R13" t="s">
         <v>117</v>
       </c>
-      <c r="S13" s="2">
+      <c r="S13">
         <v>318</v>
       </c>
-      <c r="T13" s="2">
+      <c r="T13">
         <v>2860654902513.7251</v>
       </c>
-      <c r="U13" s="2">
+      <c r="U13">
         <v>8995770133.6909599</v>
       </c>
-      <c r="V13" s="2"/>
-      <c r="W13" s="2"/>
     </row>
     <row r="14" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <v>319</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <v>3435168616790.7393</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="R14" s="3" t="s">
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="R14" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="2">
         <v>319</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="2">
         <v>3435168616790.7393</v>
       </c>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
     </row>
     <row r="15" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4" t="s">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4" t="s">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="T16" s="4" t="s">
+      <c r="T16" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="U16" s="4" t="s">
+      <c r="U16" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="V16" s="4" t="s">
+      <c r="V16" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="W16" s="4" t="s">
+      <c r="W16" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="X16" s="4" t="s">
+      <c r="X16" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="Y16" s="4" t="s">
+      <c r="Y16" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="Z16" s="4" t="s">
+      <c r="Z16" s="3" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="A17" t="s">
         <v>119</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17">
         <v>446410.58293395344</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17">
         <v>8407.7382630059928</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17">
         <v>53.095204556754318</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17">
         <v>4.0862695711507226E-160</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17">
         <v>429868.76191129786</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17">
         <v>462952.40395660902</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17">
         <v>429868.76191129786</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17">
         <v>462952.40395660902</v>
       </c>
-      <c r="R17" s="2" t="s">
+      <c r="R17" t="s">
         <v>119</v>
       </c>
-      <c r="S17" s="2">
+      <c r="S17">
         <v>560777.34544943704</v>
       </c>
-      <c r="T17" s="2">
+      <c r="T17">
         <v>15906.905953068674</v>
       </c>
-      <c r="U17" s="2">
+      <c r="U17">
         <v>35.253703460870398</v>
       </c>
-      <c r="V17" s="2">
+      <c r="V17">
         <v>6.952876876284135E-112</v>
       </c>
-      <c r="W17" s="2">
+      <c r="W17">
         <v>529481.27234763221</v>
       </c>
-      <c r="X17" s="2">
+      <c r="X17">
         <v>592073.41855124186</v>
       </c>
-      <c r="Y17" s="2">
+      <c r="Y17">
         <v>529481.27234763221</v>
       </c>
-      <c r="Z17" s="2">
+      <c r="Z17">
         <v>592073.41855124186</v>
       </c>
     </row>
     <row r="18" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="2">
         <v>35.678031072640458</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <v>1.1973782890340821</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <v>29.796791372776362</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="2">
         <v>4.7503615090054677E-94</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <v>33.322246825554025</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="2">
         <v>38.033815319726891</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="2">
         <v>33.322246825554025</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="2">
         <v>38.033815319726891</v>
       </c>
-      <c r="R18" s="3" t="s">
+      <c r="R18" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18" s="2">
         <v>2.1295753275898281</v>
       </c>
-      <c r="T18" s="3">
+      <c r="T18" s="2">
         <v>0.26647838106932348</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U18" s="2">
         <v>7.991550080138869</v>
       </c>
-      <c r="V18" s="3">
+      <c r="V18" s="2">
         <v>2.4800615101360068E-14</v>
       </c>
-      <c r="W18" s="3">
+      <c r="W18" s="2">
         <v>1.6052919176921738</v>
       </c>
-      <c r="X18" s="3">
+      <c r="X18" s="2">
         <v>2.6538587374874822</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="2">
         <v>1.6052919176921738</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="Z18" s="2">
         <v>2.6538587374874822</v>
       </c>
     </row>
@@ -64793,48 +64797,48 @@
     </row>
     <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B3" s="5"/>
+      <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4">
         <v>0.90465750254165744</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>111</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5">
         <v>0.81840519690490887</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>112</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6">
         <v>0.81069038500871216</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7">
         <v>45150.755773773897</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>320</v>
       </c>
     </row>
@@ -64844,504 +64848,502 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4" t="s">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" t="s">
         <v>116</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12">
         <v>13</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12">
         <v>2811359848226.1885</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12">
         <v>216258449863.55295</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12">
         <v>106.08232681711574</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12">
         <v>5.9466210405056933E-105</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" t="s">
         <v>117</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13">
         <v>306</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13">
         <v>623808768564.5509</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13">
         <v>2038590746.9429767</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <v>319</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <v>3435168616790.7393</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4" t="s">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="3" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="A17" t="s">
         <v>119</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17">
         <v>82258.980520192708</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17">
         <v>49817.916826846158</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17">
         <v>1.6511926985245704</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17">
         <v>9.972508642247907E-2</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17">
         <v>-15770.062789339354</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17">
         <v>180288.02382972476</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17">
         <v>-15770.062789339354</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17">
         <v>180288.02382972476</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="A18" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18">
         <v>28.515434819535241</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18">
         <v>2.5771975993061007</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18">
         <v>11.064512409608366</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18">
         <v>3.6817007967170017E-24</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18">
         <v>23.444162651377145</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18">
         <v>33.586706987693333</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18">
         <v>23.444162651377145</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18">
         <v>33.586706987693333</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="A19" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19">
         <v>2732.911563746944</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19">
         <v>1298.0837642838414</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19">
         <v>2.1053429978416713</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19">
         <v>3.6076243193731247E-2</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19">
         <v>178.61147145950508</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19">
         <v>5287.2116560343829</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19">
         <v>178.61147145950508</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I19">
         <v>5287.2116560343829</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="A20" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20">
         <v>1.155120947448981</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20">
         <v>0.13126624675622009</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20">
         <v>8.7998322188201463</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20">
         <v>1.0253632031678446E-16</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20">
         <v>0.89682221863880929</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20">
         <v>1.4134196762591527</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20">
         <v>0.89682221863880929</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I20">
         <v>1.4134196762591527</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="A21" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21">
         <v>3007.319064262756</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21">
         <v>475.98538851559522</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21">
         <v>6.3180911364555969</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21">
         <v>9.3292394265567648E-10</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21">
         <v>2070.7003688709183</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21">
         <v>3943.9377596545937</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21">
         <v>2070.7003688709183</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I21">
         <v>3943.9377596545937</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="A22" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22">
         <v>-79835.836805897867</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22">
         <v>37376.992027719985</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22">
         <v>-2.1359620577998633</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22">
         <v>3.3475926280803169E-2</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22">
         <v>-153384.29092935298</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22">
         <v>-6287.382682442767</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22">
         <v>-153384.29092935298</v>
       </c>
-      <c r="I22" s="2">
+      <c r="I22">
         <v>-6287.382682442767</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="A23" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23">
         <v>11022.300538790147</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23">
         <v>4919.6447954527976</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23">
         <v>2.240466740399226</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23">
         <v>2.5778034703065257E-2</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23">
         <v>1341.685542438694</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G23">
         <v>20702.915535141598</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23">
         <v>1341.685542438694</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23">
         <v>20702.915535141598</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="A24" t="s">
         <v>10</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24">
         <v>12953.136651058456</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24">
         <v>6855.656449025555</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24">
         <v>1.8894086579994218</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24">
         <v>5.9782322630106556E-2</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24">
         <v>-537.05896054606092</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24">
         <v>26443.332262662974</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24">
         <v>-537.05896054606092</v>
       </c>
-      <c r="I24" s="2">
+      <c r="I24">
         <v>26443.332262662974</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="A25" t="s">
         <v>102</v>
       </c>
-      <c r="B25" s="2">
-        <v>0</v>
-      </c>
-      <c r="C25" s="2">
-        <v>0</v>
-      </c>
-      <c r="D25" s="2">
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
         <v>65535</v>
       </c>
-      <c r="E25" s="2" t="e">
+      <c r="E25" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F25" s="2">
-        <v>0</v>
-      </c>
-      <c r="G25" s="2">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2">
-        <v>0</v>
-      </c>
-      <c r="I25" s="2">
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="A26" t="s">
         <v>103</v>
       </c>
-      <c r="B26" s="2">
-        <v>0</v>
-      </c>
-      <c r="C26" s="2">
-        <v>0</v>
-      </c>
-      <c r="D26" s="2">
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
         <v>65535</v>
       </c>
-      <c r="E26" s="2" t="e">
+      <c r="E26" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F26" s="2">
-        <v>0</v>
-      </c>
-      <c r="G26" s="2">
-        <v>0</v>
-      </c>
-      <c r="H26" s="2">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2">
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="A27" t="s">
         <v>104</v>
       </c>
-      <c r="B27" s="2">
-        <v>0</v>
-      </c>
-      <c r="C27" s="2">
-        <v>0</v>
-      </c>
-      <c r="D27" s="2">
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
         <v>65535</v>
       </c>
-      <c r="E27" s="2" t="e">
+      <c r="E27" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F27" s="2">
-        <v>0</v>
-      </c>
-      <c r="G27" s="2">
-        <v>0</v>
-      </c>
-      <c r="H27" s="2">
-        <v>0</v>
-      </c>
-      <c r="I27" s="2">
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="A28" t="s">
         <v>105</v>
       </c>
-      <c r="B28" s="2">
-        <v>0</v>
-      </c>
-      <c r="C28" s="2">
-        <v>0</v>
-      </c>
-      <c r="D28" s="2">
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
         <v>65535</v>
       </c>
-      <c r="E28" s="2" t="e">
+      <c r="E28" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F28" s="2">
-        <v>0</v>
-      </c>
-      <c r="G28" s="2">
-        <v>0</v>
-      </c>
-      <c r="H28" s="2">
-        <v>0</v>
-      </c>
-      <c r="I28" s="2">
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="A29" t="s">
         <v>106</v>
       </c>
-      <c r="B29" s="2">
-        <v>0</v>
-      </c>
-      <c r="C29" s="2">
-        <v>0</v>
-      </c>
-      <c r="D29" s="2">
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
         <v>65535</v>
       </c>
-      <c r="E29" s="2" t="e">
+      <c r="E29" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F29" s="2">
-        <v>0</v>
-      </c>
-      <c r="G29" s="2">
-        <v>0</v>
-      </c>
-      <c r="H29" s="2">
-        <v>0</v>
-      </c>
-      <c r="I29" s="2">
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B30" s="3">
-        <v>0</v>
-      </c>
-      <c r="C30" s="3">
-        <v>0</v>
-      </c>
-      <c r="D30" s="3">
+      <c r="B30" s="2">
+        <v>0</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2">
         <v>65535</v>
       </c>
-      <c r="E30" s="3" t="e">
+      <c r="E30" s="2" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="F30" s="3">
-        <v>0</v>
-      </c>
-      <c r="G30" s="3">
-        <v>0</v>
-      </c>
-      <c r="H30" s="3">
-        <v>0</v>
-      </c>
-      <c r="I30" s="3">
+      <c r="F30" s="2">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2">
         <v>0</v>
       </c>
     </row>
